--- a/research/traditional_assets/database/data/pakistan/pakistan_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_real_estate_operations_services.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kase_tplp" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +590,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09820000000000001</v>
+        <v>0.412</v>
       </c>
       <c r="E2">
-        <v>-0.101</v>
+        <v>0.528</v>
       </c>
       <c r="G2">
-        <v>-0.6037107516650809</v>
+        <v>0.8845725036582817</v>
       </c>
       <c r="H2">
-        <v>-0.6037107516650809</v>
+        <v>0.8845725036582817</v>
       </c>
       <c r="I2">
-        <v>-0.9286393910561371</v>
+        <v>0.7555919448122083</v>
       </c>
       <c r="J2">
-        <v>-0.7757271787383234</v>
+        <v>0.6635442141577289</v>
       </c>
       <c r="K2">
-        <v>0.6859999999999999</v>
+        <v>22.468</v>
       </c>
       <c r="L2">
-        <v>0.3263558515699334</v>
+        <v>0.7828025921538569</v>
       </c>
       <c r="M2">
-        <v>2.057</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0276140741834584</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>2.998542274052478</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>2.057</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0276140741834584</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>2.998542274052478</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>21.371</v>
+        <v>4.015</v>
       </c>
       <c r="V2">
-        <v>0.286893718704273</v>
+        <v>0.09313168332908074</v>
       </c>
       <c r="W2">
-        <v>0.05284280936454849</v>
+        <v>0.3261693738016858</v>
       </c>
       <c r="X2">
-        <v>0.08046103689844347</v>
+        <v>0.1468504595263245</v>
       </c>
       <c r="Y2">
-        <v>-0.02761822753389498</v>
+        <v>0.1793189142753613</v>
       </c>
       <c r="Z2">
-        <v>0.03344417749916469</v>
+        <v>0.7707303974221267</v>
       </c>
       <c r="AA2">
-        <v>0.02697255867431213</v>
+        <v>0.3404088883220396</v>
       </c>
       <c r="AB2">
-        <v>0.08046103689844347</v>
+        <v>0.1451863446955158</v>
       </c>
       <c r="AC2">
-        <v>-0.05348847822413134</v>
+        <v>0.1952225436265238</v>
       </c>
       <c r="AD2">
-        <v>17.3</v>
+        <v>3.55</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>17.3</v>
+        <v>3.55</v>
       </c>
       <c r="AG2">
-        <v>-4.070999999999998</v>
+        <v>-0.4649999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1884716366528309</v>
+        <v>0.07608066693812821</v>
       </c>
       <c r="AI2">
-        <v>0.2756972111553785</v>
+        <v>0.06116471399035148</v>
       </c>
       <c r="AJ2">
-        <v>-0.0578102811701221</v>
+        <v>-0.01090371898888524</v>
       </c>
       <c r="AK2">
-        <v>-0.09838323787428399</v>
+        <v>-0.00860712633040259</v>
       </c>
       <c r="AL2">
-        <v>2.11</v>
+        <v>1.44</v>
       </c>
       <c r="AM2">
-        <v>1.716</v>
+        <v>0.173</v>
       </c>
       <c r="AN2">
-        <v>-9.38177874186551</v>
+        <v>0.1614443585429078</v>
       </c>
       <c r="AO2">
-        <v>-0.9251184834123224</v>
+        <v>15.06041666666667</v>
       </c>
       <c r="AP2">
-        <v>2.207700650759218</v>
+        <v>-0.02114693710491609</v>
       </c>
       <c r="AQ2">
-        <v>-1.137529137529138</v>
+        <v>125.3583815028902</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +712,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hafiz Limited (KASE:HAFL)</t>
+          <t>TPL Properties Limited (KASE:TPLP)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,118 +721,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.147</v>
+        <v>0.647</v>
       </c>
       <c r="E3">
-        <v>-0.0128</v>
+        <v>0.753</v>
       </c>
       <c r="G3">
-        <v>0.7534246575342466</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="H3">
-        <v>0.7534246575342466</v>
+        <v>0.8873239436619719</v>
       </c>
       <c r="I3">
-        <v>0.7054794520547946</v>
+        <v>0.7570422535211268</v>
       </c>
       <c r="J3">
-        <v>0.5573287671232877</v>
+        <v>0.7408250450570723</v>
       </c>
       <c r="K3">
-        <v>0.158</v>
+        <v>22.3</v>
       </c>
       <c r="L3">
-        <v>1.082191780821918</v>
+        <v>0.7852112676056339</v>
       </c>
       <c r="M3">
-        <v>0.011</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01445466491458607</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.06962025316455696</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.011</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.01445466491458607</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.06962025316455696</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>0.021</v>
+        <v>3.57</v>
       </c>
       <c r="V3">
-        <v>0.02759526938239159</v>
+        <v>0.08419811320754716</v>
       </c>
       <c r="W3">
-        <v>0.05284280936454849</v>
+        <v>0.6211699164345404</v>
       </c>
       <c r="X3">
-        <v>0.08046103689844347</v>
+        <v>0.1499693283284512</v>
       </c>
       <c r="Y3">
-        <v>-0.02761822753389498</v>
+        <v>0.4712005881060893</v>
       </c>
       <c r="Z3">
-        <v>0.04882943143812708</v>
+        <v>0.8792569659442723</v>
       </c>
       <c r="AA3">
-        <v>0.02721404682274247</v>
+        <v>0.6513755814124103</v>
       </c>
       <c r="AB3">
-        <v>0.08046103689844347</v>
+        <v>0.1466410986668337</v>
       </c>
       <c r="AC3">
-        <v>-0.053246990075701</v>
+        <v>0.5047344827455765</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AG3">
-        <v>-0.021</v>
+        <v>-0.02000000000000002</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.07725788900979326</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.06592386258124421</v>
       </c>
       <c r="AJ3">
-        <v>-0.02837837837837838</v>
+        <v>-0.0004719207173194908</v>
       </c>
       <c r="AK3">
-        <v>-0.006910167818361303</v>
+        <v>-0.0003977724741447896</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM3">
-        <v>-0.001</v>
+        <v>0.1899999999999999</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.1628440366972477</v>
+      </c>
+      <c r="AO3">
+        <v>14.93055555555556</v>
       </c>
       <c r="AP3">
-        <v>-0.1909090909090909</v>
+        <v>-0.0009174311926605513</v>
       </c>
       <c r="AQ3">
-        <v>-103</v>
+        <v>113.1578947368421</v>
       </c>
     </row>
     <row r="4">
@@ -853,252 +852,8827 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.09820000000000001</v>
+        <v>0.177</v>
       </c>
       <c r="E4">
-        <v>-0.101</v>
+        <v>0.303</v>
       </c>
       <c r="G4">
-        <v>0.6779141104294478</v>
+        <v>0.6258278145695364</v>
       </c>
       <c r="H4">
-        <v>0.6779141104294478</v>
+        <v>0.6258278145695364</v>
       </c>
       <c r="I4">
-        <v>0.5674846625766871</v>
+        <v>0.6192052980132451</v>
       </c>
       <c r="J4">
-        <v>0.4063258762256037</v>
+        <v>0.4816041206769684</v>
       </c>
       <c r="K4">
-        <v>0.237</v>
+        <v>0.168</v>
       </c>
       <c r="L4">
-        <v>0.7269938650306748</v>
+        <v>0.5562913907284769</v>
       </c>
       <c r="M4">
-        <v>0.126</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.1223300970873786</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.5316455696202532</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>0.126</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.1223300970873786</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.5316455696202532</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="U4">
+        <v>0.445</v>
+      </c>
+      <c r="V4">
+        <v>0.6258790436005627</v>
+      </c>
+      <c r="W4">
+        <v>0.03116883116883117</v>
+      </c>
+      <c r="X4">
+        <v>0.1437315907241978</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1125627595553667</v>
+      </c>
+      <c r="Z4">
+        <v>0.0611336032388664</v>
+      </c>
+      <c r="AA4">
+        <v>0.02944219523166892</v>
+      </c>
+      <c r="AB4">
+        <v>0.1437315907241978</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1142893954925289</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-0.445</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-1.672932330827068</v>
+      </c>
+      <c r="AK4">
+        <v>-0.1188251001335113</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>-0.017</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>-2.354497354497354</v>
+      </c>
+      <c r="AQ4">
+        <v>-11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TPL Properties Limited (KASE:TPLP)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KASE:TPLP</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Real Estate (Operations &amp; Services)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0772578890097933</v>
+      </c>
+      <c r="F2">
+        <v>0.96</v>
+      </c>
+      <c r="G2">
+        <v>42.4</v>
+      </c>
+      <c r="H2">
+        <v>8.12194483294175</v>
+      </c>
+      <c r="I2">
+        <v>42.38</v>
+      </c>
+      <c r="J2">
+        <v>48.6639448329417</v>
+      </c>
+      <c r="K2">
+        <v>3.55</v>
+      </c>
+      <c r="L2">
+        <v>44.112</v>
+      </c>
+      <c r="M2">
+        <v>0.146641098666834</v>
+      </c>
+      <c r="N2">
+        <v>0.109510315866581</v>
+      </c>
+      <c r="O2">
+        <v>0.106889848623853</v>
+      </c>
+      <c r="P2">
+        <v>0.033583</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.149969328328451</v>
+      </c>
+      <c r="T2">
+        <v>1.93176589666453</v>
+      </c>
+      <c r="U2">
+        <v>0.589551551656879</v>
+      </c>
+      <c r="V2">
+        <v>10.0387489822273</v>
+      </c>
+      <c r="W2">
+        <v>10.30434925973555</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>42.4</v>
+      </c>
+      <c r="AB2">
+        <v>0.1885659159339335</v>
+      </c>
+      <c r="AC2">
+        <v>0.1505490825688073</v>
+      </c>
+      <c r="AD2">
+        <v>0.29</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>21.8</v>
+      </c>
+      <c r="AH2">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="AI2">
+        <v>1.380000000000002</v>
+      </c>
+      <c r="AJ2">
+        <v>3.55</v>
+      </c>
+      <c r="AK2">
+        <v>3.55</v>
+      </c>
+      <c r="AL2">
+        <v>1.44</v>
+      </c>
+      <c r="AM2">
+        <v>3.55</v>
+      </c>
+      <c r="AN2">
+        <v>3.57</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1437315907241978</v>
+      </c>
+      <c r="C2">
+        <v>46.38319973412274</v>
+      </c>
+      <c r="D2">
+        <v>42.81319973412274</v>
+      </c>
+      <c r="E2">
+        <v>-3.55</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>3.57</v>
+      </c>
+      <c r="H2">
+        <v>42.4</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>21.8</v>
+      </c>
+      <c r="K2">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L2">
+        <v>21.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>21.5</v>
+      </c>
+      <c r="O2">
+        <v>6.235000000000001</v>
+      </c>
+      <c r="P2">
+        <v>15.265</v>
+      </c>
+      <c r="Q2">
+        <v>15.565</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1437315907241978</v>
+      </c>
+      <c r="T2">
+        <v>0.5564716730724656</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.29</v>
+      </c>
+      <c r="W2">
+        <v>0.032447</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1433637591110976</v>
+      </c>
+      <c r="C3">
+        <v>45.97909798003314</v>
+      </c>
+      <c r="D3">
+        <v>42.86859798003314</v>
+      </c>
+      <c r="E3">
+        <v>-3.0905</v>
+      </c>
+      <c r="F3">
+        <v>0.4595</v>
+      </c>
+      <c r="G3">
+        <v>3.57</v>
+      </c>
+      <c r="H3">
+        <v>42.4</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>21.8</v>
+      </c>
+      <c r="K3">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L3">
+        <v>21.5</v>
+      </c>
+      <c r="M3">
+        <v>0.02099915</v>
+      </c>
+      <c r="N3">
+        <v>21.47900085</v>
+      </c>
+      <c r="O3">
+        <v>6.2289102465</v>
+      </c>
+      <c r="P3">
+        <v>15.2500906035</v>
+      </c>
+      <c r="Q3">
+        <v>15.5500906035</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1444841304152502</v>
+      </c>
+      <c r="T3">
+        <v>0.5604625305258135</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.29</v>
+      </c>
+      <c r="W3">
+        <v>0.032447</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>1023.850965396218</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1429959274979975</v>
+      </c>
+      <c r="C4">
+        <v>45.57513977708709</v>
+      </c>
+      <c r="D4">
+        <v>42.92413977708708</v>
+      </c>
+      <c r="E4">
+        <v>-2.631</v>
+      </c>
+      <c r="F4">
+        <v>0.9189999999999999</v>
+      </c>
+      <c r="G4">
+        <v>3.57</v>
+      </c>
+      <c r="H4">
+        <v>42.4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>21.8</v>
+      </c>
+      <c r="K4">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L4">
+        <v>21.5</v>
+      </c>
+      <c r="M4">
+        <v>0.0419983</v>
+      </c>
+      <c r="N4">
+        <v>21.4580017</v>
+      </c>
+      <c r="O4">
+        <v>6.222820493000001</v>
+      </c>
+      <c r="P4">
+        <v>15.235181207</v>
+      </c>
+      <c r="Q4">
+        <v>15.535181207</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1452520280591811</v>
+      </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.5645348340496381</v>
       </c>
       <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.29</v>
+      </c>
+      <c r="W4">
+        <v>0.032447</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>511.9254826981092</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1426280958848973</v>
+      </c>
+      <c r="C5">
+        <v>45.17132568397552</v>
+      </c>
+      <c r="D5">
+        <v>42.97982568397552</v>
+      </c>
+      <c r="E5">
+        <v>-2.1715</v>
+      </c>
+      <c r="F5">
+        <v>1.3785</v>
+      </c>
+      <c r="G5">
+        <v>3.57</v>
+      </c>
+      <c r="H5">
+        <v>42.4</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>21.8</v>
+      </c>
+      <c r="K5">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L5">
+        <v>21.5</v>
+      </c>
+      <c r="M5">
+        <v>0.06299745</v>
+      </c>
+      <c r="N5">
+        <v>21.43700255</v>
+      </c>
+      <c r="O5">
+        <v>6.216730739500001</v>
+      </c>
+      <c r="P5">
+        <v>15.2202718105</v>
+      </c>
+      <c r="Q5">
+        <v>15.5202718105</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1460357586442241</v>
+      </c>
+      <c r="T5">
+        <v>0.5686911025945723</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.29</v>
+      </c>
+      <c r="W5">
+        <v>0.032447</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>341.2836551320728</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1422602642717971</v>
+      </c>
+      <c r="C6">
+        <v>44.7676562622923</v>
+      </c>
+      <c r="D6">
+        <v>43.0356562622923</v>
+      </c>
+      <c r="E6">
+        <v>-1.712</v>
+      </c>
+      <c r="F6">
+        <v>1.838</v>
+      </c>
+      <c r="G6">
+        <v>3.57</v>
+      </c>
+      <c r="H6">
+        <v>42.4</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>21.8</v>
+      </c>
+      <c r="K6">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L6">
+        <v>21.5</v>
+      </c>
+      <c r="M6">
+        <v>0.0839966</v>
+      </c>
+      <c r="N6">
+        <v>21.4160034</v>
+      </c>
+      <c r="O6">
+        <v>6.210640986000001</v>
+      </c>
+      <c r="P6">
+        <v>15.205362414</v>
+      </c>
+      <c r="Q6">
+        <v>15.505362414</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1468358169497887</v>
+      </c>
+      <c r="T6">
+        <v>0.5729339600675261</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.29</v>
+      </c>
+      <c r="W6">
+        <v>0.032447</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>255.9627413490546</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.141892432658697</v>
+      </c>
+      <c r="C7">
+        <v>44.36413207655309</v>
+      </c>
+      <c r="D7">
+        <v>43.09163207655309</v>
+      </c>
+      <c r="E7">
+        <v>-1.2525</v>
+      </c>
+      <c r="F7">
+        <v>2.2975</v>
+      </c>
+      <c r="G7">
+        <v>3.57</v>
+      </c>
+      <c r="H7">
+        <v>42.4</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>21.8</v>
+      </c>
+      <c r="K7">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L7">
+        <v>21.5</v>
+      </c>
+      <c r="M7">
+        <v>0.10499575</v>
+      </c>
+      <c r="N7">
+        <v>21.39500425</v>
+      </c>
+      <c r="O7">
+        <v>6.204551232500001</v>
+      </c>
+      <c r="P7">
+        <v>15.1904530175</v>
+      </c>
+      <c r="Q7">
+        <v>15.4904530175</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1476527185881021</v>
+      </c>
+      <c r="T7">
+        <v>0.5772661408556998</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.29</v>
+      </c>
+      <c r="W7">
+        <v>0.032447</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>204.7701930792437</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1415246010455968</v>
+      </c>
+      <c r="C8">
+        <v>43.96075369421444</v>
+      </c>
+      <c r="D8">
+        <v>43.14775369421444</v>
+      </c>
+      <c r="E8">
+        <v>-0.7930000000000001</v>
+      </c>
+      <c r="F8">
+        <v>2.757</v>
+      </c>
+      <c r="G8">
+        <v>3.57</v>
+      </c>
+      <c r="H8">
+        <v>42.4</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>21.8</v>
+      </c>
+      <c r="K8">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L8">
+        <v>21.5</v>
+      </c>
+      <c r="M8">
+        <v>0.1259949</v>
+      </c>
+      <c r="N8">
+        <v>21.3740051</v>
+      </c>
+      <c r="O8">
+        <v>6.198461479000001</v>
+      </c>
+      <c r="P8">
+        <v>15.175543621</v>
+      </c>
+      <c r="Q8">
+        <v>15.475543621</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.148487001112337</v>
+      </c>
+      <c r="T8">
+        <v>0.5816904957031964</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.29</v>
+      </c>
+      <c r="W8">
+        <v>0.032447</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>170.6418275660364</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1411567694324966</v>
+      </c>
+      <c r="C9">
+        <v>43.55752168569292</v>
+      </c>
+      <c r="D9">
+        <v>43.20402168569291</v>
+      </c>
+      <c r="E9">
+        <v>-0.3334999999999999</v>
+      </c>
+      <c r="F9">
+        <v>3.2165</v>
+      </c>
+      <c r="G9">
+        <v>3.57</v>
+      </c>
+      <c r="H9">
+        <v>42.4</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>21.8</v>
+      </c>
+      <c r="K9">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L9">
+        <v>21.5</v>
+      </c>
+      <c r="M9">
+        <v>0.14699405</v>
+      </c>
+      <c r="N9">
+        <v>21.35300595</v>
+      </c>
+      <c r="O9">
+        <v>6.192371725500001</v>
+      </c>
+      <c r="P9">
+        <v>15.1606342245</v>
+      </c>
+      <c r="Q9">
+        <v>15.4606342245</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1493392251962329</v>
+      </c>
+      <c r="T9">
+        <v>0.5862099979667683</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.29</v>
+      </c>
+      <c r="W9">
+        <v>0.032447</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>146.2644236280312</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1407889378193965</v>
+      </c>
+      <c r="C10">
+        <v>43.15443662438444</v>
+      </c>
+      <c r="D10">
+        <v>43.26043662438444</v>
+      </c>
+      <c r="E10">
+        <v>0.1259999999999999</v>
+      </c>
+      <c r="F10">
+        <v>3.676</v>
+      </c>
+      <c r="G10">
+        <v>3.57</v>
+      </c>
+      <c r="H10">
+        <v>42.4</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>21.8</v>
+      </c>
+      <c r="K10">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L10">
+        <v>21.5</v>
+      </c>
+      <c r="M10">
+        <v>0.1679932</v>
+      </c>
+      <c r="N10">
+        <v>21.3320068</v>
+      </c>
+      <c r="O10">
+        <v>6.186281972000001</v>
+      </c>
+      <c r="P10">
+        <v>15.145724828</v>
+      </c>
+      <c r="Q10">
+        <v>15.445724828</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1502099758906483</v>
+      </c>
+      <c r="T10">
+        <v>0.5908277502795481</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.29</v>
+      </c>
+      <c r="W10">
+        <v>0.032447</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>127.9813706745273</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1404211062062963</v>
+      </c>
+      <c r="C11">
+        <v>42.75149908668376</v>
+      </c>
+      <c r="D11">
+        <v>43.31699908668377</v>
+      </c>
+      <c r="E11">
+        <v>0.5854999999999997</v>
+      </c>
+      <c r="F11">
+        <v>4.1355</v>
+      </c>
+      <c r="G11">
+        <v>3.57</v>
+      </c>
+      <c r="H11">
+        <v>42.4</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>21.8</v>
+      </c>
+      <c r="K11">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L11">
+        <v>21.5</v>
+      </c>
+      <c r="M11">
+        <v>0.18899235</v>
+      </c>
+      <c r="N11">
+        <v>21.31100765</v>
+      </c>
+      <c r="O11">
+        <v>6.180192218500001</v>
+      </c>
+      <c r="P11">
+        <v>15.1308154315</v>
+      </c>
+      <c r="Q11">
+        <v>15.4308154315</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1510998639629629</v>
+      </c>
+      <c r="T11">
+        <v>0.5955469916541475</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.29</v>
+      </c>
+      <c r="W11">
+        <v>0.032447</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>113.7612183773576</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1400532745931961</v>
+      </c>
+      <c r="C12">
+        <v>42.3487096520041</v>
+      </c>
+      <c r="D12">
+        <v>43.3737096520041</v>
+      </c>
+      <c r="E12">
+        <v>1.045</v>
+      </c>
+      <c r="F12">
+        <v>4.595</v>
+      </c>
+      <c r="G12">
+        <v>3.57</v>
+      </c>
+      <c r="H12">
+        <v>42.4</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>21.8</v>
+      </c>
+      <c r="K12">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L12">
+        <v>21.5</v>
+      </c>
+      <c r="M12">
+        <v>0.2099915</v>
+      </c>
+      <c r="N12">
+        <v>21.2900085</v>
+      </c>
+      <c r="O12">
+        <v>6.174102465000001</v>
+      </c>
+      <c r="P12">
+        <v>15.115906035</v>
+      </c>
+      <c r="Q12">
+        <v>15.415906035</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1520095273257734</v>
+      </c>
+      <c r="T12">
+        <v>0.6003711050592934</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.29</v>
+      </c>
+      <c r="W12">
+        <v>0.032447</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>102.3850965396218</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1396854429800959</v>
+      </c>
+      <c r="C13">
+        <v>41.94606890279689</v>
+      </c>
+      <c r="D13">
+        <v>43.43056890279689</v>
+      </c>
+      <c r="E13">
+        <v>1.5045</v>
+      </c>
+      <c r="F13">
+        <v>5.0545</v>
+      </c>
+      <c r="G13">
+        <v>3.57</v>
+      </c>
+      <c r="H13">
+        <v>42.4</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>21.8</v>
+      </c>
+      <c r="K13">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L13">
+        <v>21.5</v>
+      </c>
+      <c r="M13">
+        <v>0.23099065</v>
+      </c>
+      <c r="N13">
+        <v>21.26900935</v>
+      </c>
+      <c r="O13">
+        <v>6.168012711500001</v>
+      </c>
+      <c r="P13">
+        <v>15.1009966385</v>
+      </c>
+      <c r="Q13">
+        <v>15.4009966385</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1529396325619055</v>
+      </c>
+      <c r="T13">
+        <v>0.6053036255072516</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.29</v>
+      </c>
+      <c r="W13">
+        <v>0.032447</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>93.07736049056531</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1393176113669958</v>
+      </c>
+      <c r="C14">
+        <v>41.54357742457179</v>
+      </c>
+      <c r="D14">
+        <v>43.4875774245718</v>
+      </c>
+      <c r="E14">
+        <v>1.964</v>
+      </c>
+      <c r="F14">
+        <v>5.513999999999999</v>
+      </c>
+      <c r="G14">
+        <v>3.57</v>
+      </c>
+      <c r="H14">
+        <v>42.4</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>21.8</v>
+      </c>
+      <c r="K14">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L14">
+        <v>21.5</v>
+      </c>
+      <c r="M14">
+        <v>0.2519898</v>
+      </c>
+      <c r="N14">
+        <v>21.2480102</v>
+      </c>
+      <c r="O14">
+        <v>6.161922958000001</v>
+      </c>
+      <c r="P14">
+        <v>15.086087242</v>
+      </c>
+      <c r="Q14">
+        <v>15.386087242</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1538908765534043</v>
+      </c>
+      <c r="T14">
+        <v>0.6103482486926634</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.29</v>
+      </c>
+      <c r="W14">
+        <v>0.032447</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>85.3209137830182</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1389497797538956</v>
+      </c>
+      <c r="C15">
+        <v>41.14123580591676</v>
+      </c>
+      <c r="D15">
+        <v>43.54473580591676</v>
+      </c>
+      <c r="E15">
+        <v>2.4235</v>
+      </c>
+      <c r="F15">
+        <v>5.9735</v>
+      </c>
+      <c r="G15">
+        <v>3.57</v>
+      </c>
+      <c r="H15">
+        <v>42.4</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>21.8</v>
+      </c>
+      <c r="K15">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L15">
+        <v>21.5</v>
+      </c>
+      <c r="M15">
+        <v>0.27298895</v>
+      </c>
+      <c r="N15">
+        <v>21.22701105</v>
+      </c>
+      <c r="O15">
+        <v>6.155833204500001</v>
+      </c>
+      <c r="P15">
+        <v>15.0711778455</v>
+      </c>
+      <c r="Q15">
+        <v>15.3711778455</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1548639882228685</v>
+      </c>
+      <c r="T15">
+        <v>0.6155088402271651</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.29</v>
+      </c>
+      <c r="W15">
+        <v>0.032447</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>78.75776656893989</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1385819481407954</v>
+      </c>
+      <c r="C16">
+        <v>40.73904463851822</v>
+      </c>
+      <c r="D16">
+        <v>43.60204463851822</v>
+      </c>
+      <c r="E16">
+        <v>2.883</v>
+      </c>
+      <c r="F16">
+        <v>6.433</v>
+      </c>
+      <c r="G16">
+        <v>3.57</v>
+      </c>
+      <c r="H16">
+        <v>42.4</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>21.8</v>
+      </c>
+      <c r="K16">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L16">
+        <v>21.5</v>
+      </c>
+      <c r="M16">
+        <v>0.2939881</v>
+      </c>
+      <c r="N16">
+        <v>21.2060119</v>
+      </c>
+      <c r="O16">
+        <v>6.149743451000001</v>
+      </c>
+      <c r="P16">
+        <v>15.056268449</v>
+      </c>
+      <c r="Q16">
+        <v>15.356268449</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1558597303962737</v>
+      </c>
+      <c r="T16">
+        <v>0.6207894455182831</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.29</v>
+      </c>
+      <c r="W16">
+        <v>0.032447</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>73.13221181401559</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1382141165276952</v>
+      </c>
+      <c r="C17">
+        <v>40.33700451718163</v>
+      </c>
+      <c r="D17">
+        <v>43.65950451718163</v>
+      </c>
+      <c r="E17">
+        <v>3.342499999999999</v>
+      </c>
+      <c r="F17">
+        <v>6.892499999999999</v>
+      </c>
+      <c r="G17">
+        <v>3.57</v>
+      </c>
+      <c r="H17">
+        <v>42.4</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>21.8</v>
+      </c>
+      <c r="K17">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L17">
+        <v>21.5</v>
+      </c>
+      <c r="M17">
+        <v>0.31498725</v>
+      </c>
+      <c r="N17">
+        <v>21.18501275</v>
+      </c>
+      <c r="O17">
+        <v>6.1436536975</v>
+      </c>
+      <c r="P17">
+        <v>15.0413590525</v>
+      </c>
+      <c r="Q17">
+        <v>15.3413590525</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1568789017972885</v>
+      </c>
+      <c r="T17">
+        <v>0.6261943003456627</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.29</v>
+      </c>
+      <c r="W17">
+        <v>0.032447</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>68.25673102641456</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1378462849145951</v>
+      </c>
+      <c r="C18">
+        <v>39.93511603985196</v>
+      </c>
+      <c r="D18">
+        <v>43.71711603985195</v>
+      </c>
+      <c r="E18">
+        <v>3.802</v>
+      </c>
+      <c r="F18">
+        <v>7.351999999999999</v>
+      </c>
+      <c r="G18">
+        <v>3.57</v>
+      </c>
+      <c r="H18">
+        <v>42.4</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>21.8</v>
+      </c>
+      <c r="K18">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L18">
+        <v>21.5</v>
+      </c>
+      <c r="M18">
+        <v>0.3359864</v>
+      </c>
+      <c r="N18">
+        <v>21.1640136</v>
+      </c>
+      <c r="O18">
+        <v>6.137563944000001</v>
+      </c>
+      <c r="P18">
+        <v>15.026449656</v>
+      </c>
+      <c r="Q18">
+        <v>15.326449656</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1579223391840417</v>
+      </c>
+      <c r="T18">
+        <v>0.6317278421927418</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.29</v>
+      </c>
+      <c r="W18">
+        <v>0.032447</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>63.99068533726365</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1374784533014949</v>
+      </c>
+      <c r="C19">
+        <v>39.53337980763441</v>
+      </c>
+      <c r="D19">
+        <v>43.77487980763441</v>
+      </c>
+      <c r="E19">
+        <v>4.2615</v>
+      </c>
+      <c r="F19">
+        <v>7.8115</v>
+      </c>
+      <c r="G19">
+        <v>3.57</v>
+      </c>
+      <c r="H19">
+        <v>42.4</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>21.8</v>
+      </c>
+      <c r="K19">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L19">
+        <v>21.5</v>
+      </c>
+      <c r="M19">
+        <v>0.35698555</v>
+      </c>
+      <c r="N19">
+        <v>21.14301445</v>
+      </c>
+      <c r="O19">
+        <v>6.131474190500001</v>
+      </c>
+      <c r="P19">
+        <v>15.0115402595</v>
+      </c>
+      <c r="Q19">
+        <v>15.3115402595</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1589909196403553</v>
+      </c>
+      <c r="T19">
+        <v>0.637394722397582</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.29</v>
+      </c>
+      <c r="W19">
+        <v>0.032447</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>60.22652737624814</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1371106216883947</v>
+      </c>
+      <c r="C20">
+        <v>39.13179642481546</v>
+      </c>
+      <c r="D20">
+        <v>43.83279642481546</v>
+      </c>
+      <c r="E20">
+        <v>4.720999999999999</v>
+      </c>
+      <c r="F20">
+        <v>8.270999999999999</v>
+      </c>
+      <c r="G20">
+        <v>3.57</v>
+      </c>
+      <c r="H20">
+        <v>42.4</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>21.8</v>
+      </c>
+      <c r="K20">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L20">
+        <v>21.5</v>
+      </c>
+      <c r="M20">
+        <v>0.3779847</v>
+      </c>
+      <c r="N20">
+        <v>21.1220153</v>
+      </c>
+      <c r="O20">
+        <v>6.125384437000001</v>
+      </c>
+      <c r="P20">
+        <v>14.996630863</v>
+      </c>
+      <c r="Q20">
+        <v>15.296630863</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1600855630346277</v>
+      </c>
+      <c r="T20">
+        <v>0.6431998191927839</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.29</v>
+      </c>
+      <c r="W20">
+        <v>0.032447</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>56.8806091886788</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1367427900752946</v>
+      </c>
+      <c r="C21">
+        <v>38.73036649888374</v>
+      </c>
+      <c r="D21">
+        <v>43.89086649888374</v>
+      </c>
+      <c r="E21">
+        <v>5.180499999999999</v>
+      </c>
+      <c r="F21">
+        <v>8.730499999999999</v>
+      </c>
+      <c r="G21">
+        <v>3.57</v>
+      </c>
+      <c r="H21">
+        <v>42.4</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>21.8</v>
+      </c>
+      <c r="K21">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L21">
+        <v>21.5</v>
+      </c>
+      <c r="M21">
+        <v>0.39898385</v>
+      </c>
+      <c r="N21">
+        <v>21.10101615</v>
+      </c>
+      <c r="O21">
+        <v>6.119294683500001</v>
+      </c>
+      <c r="P21">
+        <v>14.9817214665</v>
+      </c>
+      <c r="Q21">
+        <v>15.2817214665</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1612072346608575</v>
+      </c>
+      <c r="T21">
+        <v>0.6491482517113243</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.29</v>
+      </c>
+      <c r="W21">
+        <v>0.032447</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>53.88689291559044</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1363749584621944</v>
+      </c>
+      <c r="C22">
+        <v>38.32909064055146</v>
+      </c>
+      <c r="D22">
+        <v>43.94909064055146</v>
+      </c>
+      <c r="E22">
+        <v>5.64</v>
+      </c>
+      <c r="F22">
+        <v>9.19</v>
+      </c>
+      <c r="G22">
+        <v>3.57</v>
+      </c>
+      <c r="H22">
+        <v>42.4</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>21.8</v>
+      </c>
+      <c r="K22">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L22">
+        <v>21.5</v>
+      </c>
+      <c r="M22">
+        <v>0.419983</v>
+      </c>
+      <c r="N22">
+        <v>21.080017</v>
+      </c>
+      <c r="O22">
+        <v>6.113204930000001</v>
+      </c>
+      <c r="P22">
+        <v>14.96681207</v>
+      </c>
+      <c r="Q22">
+        <v>15.26681207</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.162356948077743</v>
+      </c>
+      <c r="T22">
+        <v>0.6552453950428282</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.29</v>
+      </c>
+      <c r="W22">
+        <v>0.032447</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>51.19254826981093</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1360071268490942</v>
+      </c>
+      <c r="C23">
+        <v>37.9279694637757</v>
+      </c>
+      <c r="D23">
+        <v>44.00746946377569</v>
+      </c>
+      <c r="E23">
+        <v>6.099499999999998</v>
+      </c>
+      <c r="F23">
+        <v>9.649499999999998</v>
+      </c>
+      <c r="G23">
+        <v>3.57</v>
+      </c>
+      <c r="H23">
+        <v>42.4</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>21.8</v>
+      </c>
+      <c r="K23">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L23">
+        <v>21.5</v>
+      </c>
+      <c r="M23">
+        <v>0.44098215</v>
+      </c>
+      <c r="N23">
+        <v>21.05901785</v>
+      </c>
+      <c r="O23">
+        <v>6.107115176500001</v>
+      </c>
+      <c r="P23">
+        <v>14.9519026735</v>
+      </c>
+      <c r="Q23">
+        <v>15.2519026735</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1635357681634104</v>
+      </c>
+      <c r="T23">
+        <v>0.6614968964333575</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.29</v>
+      </c>
+      <c r="W23">
+        <v>0.032447</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>48.7548078760104</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.135639295235994</v>
+      </c>
+      <c r="C24">
+        <v>37.52700358578</v>
+      </c>
+      <c r="D24">
+        <v>44.06600358578</v>
+      </c>
+      <c r="E24">
+        <v>6.559</v>
+      </c>
+      <c r="F24">
+        <v>10.109</v>
+      </c>
+      <c r="G24">
+        <v>3.57</v>
+      </c>
+      <c r="H24">
+        <v>42.4</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>21.8</v>
+      </c>
+      <c r="K24">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L24">
+        <v>21.5</v>
+      </c>
+      <c r="M24">
+        <v>0.4619813</v>
+      </c>
+      <c r="N24">
+        <v>21.0380187</v>
+      </c>
+      <c r="O24">
+        <v>6.101025423</v>
+      </c>
+      <c r="P24">
+        <v>14.936993277</v>
+      </c>
+      <c r="Q24">
+        <v>15.236993277</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1647448144051205</v>
+      </c>
+      <c r="T24">
+        <v>0.6679086927313362</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.29</v>
+      </c>
+      <c r="W24">
+        <v>0.032447</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>46.53868024528265</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1352714636228939</v>
+      </c>
+      <c r="C25">
+        <v>37.1261936270762</v>
+      </c>
+      <c r="D25">
+        <v>44.1246936270762</v>
+      </c>
+      <c r="E25">
+        <v>7.0185</v>
+      </c>
+      <c r="F25">
+        <v>10.5685</v>
+      </c>
+      <c r="G25">
+        <v>3.57</v>
+      </c>
+      <c r="H25">
+        <v>42.4</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>21.8</v>
+      </c>
+      <c r="K25">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L25">
+        <v>21.5</v>
+      </c>
+      <c r="M25">
+        <v>0.4829804500000001</v>
+      </c>
+      <c r="N25">
+        <v>21.01701955</v>
+      </c>
+      <c r="O25">
+        <v>6.094935669500001</v>
+      </c>
+      <c r="P25">
+        <v>14.9220838805</v>
+      </c>
+      <c r="Q25">
+        <v>15.2220838805</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1659852644453167</v>
+      </c>
+      <c r="T25">
+        <v>0.6744870291928989</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.29</v>
+      </c>
+      <c r="W25">
+        <v>0.032447</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>44.51525936505297</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1349036320097937</v>
+      </c>
+      <c r="C26">
+        <v>36.72554021148625</v>
+      </c>
+      <c r="D26">
+        <v>44.18354021148625</v>
+      </c>
+      <c r="E26">
+        <v>7.477999999999999</v>
+      </c>
+      <c r="F26">
+        <v>11.028</v>
+      </c>
+      <c r="G26">
+        <v>3.57</v>
+      </c>
+      <c r="H26">
+        <v>42.4</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>21.8</v>
+      </c>
+      <c r="K26">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L26">
+        <v>21.5</v>
+      </c>
+      <c r="M26">
+        <v>0.5039796</v>
+      </c>
+      <c r="N26">
+        <v>20.9960204</v>
+      </c>
+      <c r="O26">
+        <v>6.088845916</v>
+      </c>
+      <c r="P26">
+        <v>14.907174484</v>
+      </c>
+      <c r="Q26">
+        <v>15.207174484</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1672583579076233</v>
+      </c>
+      <c r="T26">
+        <v>0.681238479771871</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.29</v>
+      </c>
+      <c r="W26">
+        <v>0.032447</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>42.6604568915091</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1345358003966935</v>
+      </c>
+      <c r="C27">
+        <v>36.32504396616442</v>
+      </c>
+      <c r="D27">
+        <v>44.24254396616441</v>
+      </c>
+      <c r="E27">
+        <v>7.937499999999999</v>
+      </c>
+      <c r="F27">
+        <v>11.4875</v>
+      </c>
+      <c r="G27">
+        <v>3.57</v>
+      </c>
+      <c r="H27">
+        <v>42.4</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>21.8</v>
+      </c>
+      <c r="K27">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L27">
+        <v>21.5</v>
+      </c>
+      <c r="M27">
+        <v>0.52497875</v>
+      </c>
+      <c r="N27">
+        <v>20.97502125</v>
+      </c>
+      <c r="O27">
+        <v>6.082756162500001</v>
+      </c>
+      <c r="P27">
+        <v>14.8922650875</v>
+      </c>
+      <c r="Q27">
+        <v>15.1922650875</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1685654005289247</v>
+      </c>
+      <c r="T27">
+        <v>0.688169969032949</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.29</v>
+      </c>
+      <c r="W27">
+        <v>0.032447</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>40.95403861584874</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1341679687835933</v>
+      </c>
+      <c r="C28">
+        <v>35.92470552161943</v>
+      </c>
+      <c r="D28">
+        <v>44.30170552161943</v>
+      </c>
+      <c r="E28">
+        <v>8.396999999999998</v>
+      </c>
+      <c r="F28">
+        <v>11.947</v>
+      </c>
+      <c r="G28">
+        <v>3.57</v>
+      </c>
+      <c r="H28">
+        <v>42.4</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>21.8</v>
+      </c>
+      <c r="K28">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L28">
+        <v>21.5</v>
+      </c>
+      <c r="M28">
+        <v>0.5459779</v>
+      </c>
+      <c r="N28">
+        <v>20.9540221</v>
+      </c>
+      <c r="O28">
+        <v>6.076666409</v>
+      </c>
+      <c r="P28">
+        <v>14.877355691</v>
+      </c>
+      <c r="Q28">
+        <v>15.177355691</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1699077686264775</v>
+      </c>
+      <c r="T28">
+        <v>0.695288795841624</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.29</v>
+      </c>
+      <c r="W28">
+        <v>0.032447</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>39.37888328446994</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1338001371704932</v>
+      </c>
+      <c r="C29">
+        <v>35.52452551173713</v>
+      </c>
+      <c r="D29">
+        <v>44.36102551173713</v>
+      </c>
+      <c r="E29">
+        <v>8.8565</v>
+      </c>
+      <c r="F29">
+        <v>12.4065</v>
+      </c>
+      <c r="G29">
+        <v>3.57</v>
+      </c>
+      <c r="H29">
+        <v>42.4</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>21.8</v>
+      </c>
+      <c r="K29">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L29">
+        <v>21.5</v>
+      </c>
+      <c r="M29">
+        <v>0.56697705</v>
+      </c>
+      <c r="N29">
+        <v>20.93302295</v>
+      </c>
+      <c r="O29">
+        <v>6.070576655500001</v>
+      </c>
+      <c r="P29">
+        <v>14.8624462945</v>
+      </c>
+      <c r="Q29">
+        <v>15.1624462945</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1712869139321824</v>
+      </c>
+      <c r="T29">
+        <v>0.7026026590012212</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.29</v>
+      </c>
+      <c r="W29">
+        <v>0.032447</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>37.92040612578587</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.133432305557393</v>
+      </c>
+      <c r="C30">
+        <v>35.12450457380292</v>
+      </c>
+      <c r="D30">
+        <v>44.42050457380292</v>
+      </c>
+      <c r="E30">
+        <v>9.315999999999999</v>
+      </c>
+      <c r="F30">
+        <v>12.866</v>
+      </c>
+      <c r="G30">
+        <v>3.57</v>
+      </c>
+      <c r="H30">
+        <v>42.4</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>21.8</v>
+      </c>
+      <c r="K30">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L30">
+        <v>21.5</v>
+      </c>
+      <c r="M30">
+        <v>0.5879762000000001</v>
+      </c>
+      <c r="N30">
+        <v>20.9120238</v>
+      </c>
+      <c r="O30">
+        <v>6.064486902000001</v>
+      </c>
+      <c r="P30">
+        <v>14.847536898</v>
+      </c>
+      <c r="Q30">
+        <v>15.147536898</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1727043688297125</v>
+      </c>
+      <c r="T30">
+        <v>0.7101196850263631</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.29</v>
+      </c>
+      <c r="W30">
+        <v>0.032447</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>36.5661059070078</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1330644739442928</v>
+      </c>
+      <c r="C31">
+        <v>34.72464334852472</v>
+      </c>
+      <c r="D31">
+        <v>44.48014334852471</v>
+      </c>
+      <c r="E31">
+        <v>9.775499999999997</v>
+      </c>
+      <c r="F31">
+        <v>13.3255</v>
+      </c>
+      <c r="G31">
+        <v>3.57</v>
+      </c>
+      <c r="H31">
+        <v>42.4</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>21.8</v>
+      </c>
+      <c r="K31">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L31">
+        <v>21.5</v>
+      </c>
+      <c r="M31">
+        <v>0.60897535</v>
+      </c>
+      <c r="N31">
+        <v>20.89102465</v>
+      </c>
+      <c r="O31">
+        <v>6.0583971485</v>
+      </c>
+      <c r="P31">
+        <v>14.8326275015</v>
+      </c>
+      <c r="Q31">
+        <v>15.1326275015</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1741617520342152</v>
+      </c>
+      <c r="T31">
+        <v>0.7178484582634806</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.29</v>
+      </c>
+      <c r="W31">
+        <v>0.032447</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>35.30520570331787</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1326966423311926</v>
+      </c>
+      <c r="C32">
+        <v>34.32494248005589</v>
+      </c>
+      <c r="D32">
+        <v>44.53994248005588</v>
+      </c>
+      <c r="E32">
+        <v>10.235</v>
+      </c>
+      <c r="F32">
+        <v>13.785</v>
+      </c>
+      <c r="G32">
+        <v>3.57</v>
+      </c>
+      <c r="H32">
+        <v>42.4</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>21.8</v>
+      </c>
+      <c r="K32">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L32">
+        <v>21.5</v>
+      </c>
+      <c r="M32">
+        <v>0.6299745</v>
+      </c>
+      <c r="N32">
+        <v>20.8700255</v>
+      </c>
+      <c r="O32">
+        <v>6.052307395000001</v>
+      </c>
+      <c r="P32">
+        <v>14.817718105</v>
+      </c>
+      <c r="Q32">
+        <v>15.117718105</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1756607747588466</v>
+      </c>
+      <c r="T32">
+        <v>0.7257980535930872</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.29</v>
+      </c>
+      <c r="W32">
+        <v>0.032447</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>34.12836551320729</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1323288107180924</v>
+      </c>
+      <c r="C33">
+        <v>33.92540261601847</v>
+      </c>
+      <c r="D33">
+        <v>44.59990261601848</v>
+      </c>
+      <c r="E33">
+        <v>10.6945</v>
+      </c>
+      <c r="F33">
+        <v>14.2445</v>
+      </c>
+      <c r="G33">
+        <v>3.57</v>
+      </c>
+      <c r="H33">
+        <v>42.4</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>21.8</v>
+      </c>
+      <c r="K33">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L33">
+        <v>21.5</v>
+      </c>
+      <c r="M33">
+        <v>0.65097365</v>
+      </c>
+      <c r="N33">
+        <v>20.84902635</v>
+      </c>
+      <c r="O33">
+        <v>6.0462176415</v>
+      </c>
+      <c r="P33">
+        <v>14.8028087085</v>
+      </c>
+      <c r="Q33">
+        <v>15.1028087085</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1772032474175253</v>
+      </c>
+      <c r="T33">
+        <v>0.733978071975726</v>
+      </c>
+      <c r="U33">
+        <v>0.0457</v>
+      </c>
+      <c r="V33">
+        <v>0.29</v>
+      </c>
+      <c r="W33">
+        <v>0.032447</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>33.02745049665221</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1319609791049923</v>
+      </c>
+      <c r="C34">
+        <v>33.52602440752653</v>
+      </c>
+      <c r="D34">
+        <v>44.66002440752654</v>
+      </c>
+      <c r="E34">
+        <v>11.154</v>
+      </c>
+      <c r="F34">
+        <v>14.704</v>
+      </c>
+      <c r="G34">
+        <v>3.57</v>
+      </c>
+      <c r="H34">
+        <v>42.4</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>21.8</v>
+      </c>
+      <c r="K34">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L34">
+        <v>21.5</v>
+      </c>
+      <c r="M34">
+        <v>0.6719728</v>
+      </c>
+      <c r="N34">
+        <v>20.8280272</v>
+      </c>
+      <c r="O34">
+        <v>6.040127888000001</v>
+      </c>
+      <c r="P34">
+        <v>14.787899312</v>
+      </c>
+      <c r="Q34">
+        <v>15.087899312</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1787910869191063</v>
+      </c>
+      <c r="T34">
+        <v>0.7423986791343248</v>
+      </c>
+      <c r="U34">
+        <v>0.0457</v>
+      </c>
+      <c r="V34">
+        <v>0.29</v>
+      </c>
+      <c r="W34">
+        <v>0.032447</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>31.99534266863182</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1315931474918921</v>
+      </c>
+      <c r="C35">
+        <v>33.12680850920979</v>
+      </c>
+      <c r="D35">
+        <v>44.72030850920979</v>
+      </c>
+      <c r="E35">
+        <v>11.6135</v>
+      </c>
+      <c r="F35">
+        <v>15.1635</v>
+      </c>
+      <c r="G35">
+        <v>3.57</v>
+      </c>
+      <c r="H35">
+        <v>42.4</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>21.8</v>
+      </c>
+      <c r="K35">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L35">
+        <v>21.5</v>
+      </c>
+      <c r="M35">
+        <v>0.69297195</v>
+      </c>
+      <c r="N35">
+        <v>20.80702805</v>
+      </c>
+      <c r="O35">
+        <v>6.0340381345</v>
+      </c>
+      <c r="P35">
+        <v>14.7729899155</v>
+      </c>
+      <c r="Q35">
+        <v>15.0729899155</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1804263246147643</v>
+      </c>
+      <c r="T35">
+        <v>0.7510706477006427</v>
+      </c>
+      <c r="U35">
+        <v>0.0457</v>
+      </c>
+      <c r="V35">
+        <v>0.29</v>
+      </c>
+      <c r="W35">
+        <v>0.032447</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>31.02578683018844</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1312253158787919</v>
+      </c>
+      <c r="C36">
+        <v>32.72775557923731</v>
+      </c>
+      <c r="D36">
+        <v>44.78075557923731</v>
+      </c>
+      <c r="E36">
+        <v>12.073</v>
+      </c>
+      <c r="F36">
+        <v>15.623</v>
+      </c>
+      <c r="G36">
+        <v>3.57</v>
+      </c>
+      <c r="H36">
+        <v>42.4</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>21.8</v>
+      </c>
+      <c r="K36">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L36">
+        <v>21.5</v>
+      </c>
+      <c r="M36">
+        <v>0.7139711000000001</v>
+      </c>
+      <c r="N36">
+        <v>20.7860289</v>
+      </c>
+      <c r="O36">
+        <v>6.027948381000002</v>
+      </c>
+      <c r="P36">
+        <v>14.758080519</v>
+      </c>
+      <c r="Q36">
+        <v>15.058080519</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1821111149678666</v>
+      </c>
+      <c r="T36">
+        <v>0.7600054031932129</v>
+      </c>
+      <c r="U36">
+        <v>0.0457</v>
+      </c>
+      <c r="V36">
+        <v>0.29</v>
+      </c>
+      <c r="W36">
+        <v>0.032447</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>30.11326368812407</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1308574842656918</v>
+      </c>
+      <c r="C37">
+        <v>32.32886627934144</v>
+      </c>
+      <c r="D37">
+        <v>44.84136627934144</v>
+      </c>
+      <c r="E37">
+        <v>12.5325</v>
+      </c>
+      <c r="F37">
+        <v>16.0825</v>
+      </c>
+      <c r="G37">
+        <v>3.57</v>
+      </c>
+      <c r="H37">
+        <v>42.4</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>21.8</v>
+      </c>
+      <c r="K37">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L37">
+        <v>21.5</v>
+      </c>
+      <c r="M37">
+        <v>0.73497025</v>
+      </c>
+      <c r="N37">
+        <v>20.76502975</v>
+      </c>
+      <c r="O37">
+        <v>6.0218586275</v>
+      </c>
+      <c r="P37">
+        <v>14.7431711225</v>
+      </c>
+      <c r="Q37">
+        <v>15.0431711225</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1838477450241412</v>
+      </c>
+      <c r="T37">
+        <v>0.7692150742394006</v>
+      </c>
+      <c r="U37">
+        <v>0.0457</v>
+      </c>
+      <c r="V37">
+        <v>0.29</v>
+      </c>
+      <c r="W37">
+        <v>0.032447</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>29.25288472560624</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1304896526525916</v>
+      </c>
+      <c r="C38">
+        <v>31.93014127484208</v>
+      </c>
+      <c r="D38">
+        <v>44.90214127484207</v>
+      </c>
+      <c r="E38">
+        <v>12.992</v>
+      </c>
+      <c r="F38">
+        <v>16.542</v>
+      </c>
+      <c r="G38">
+        <v>3.57</v>
+      </c>
+      <c r="H38">
+        <v>42.4</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>21.8</v>
+      </c>
+      <c r="K38">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L38">
+        <v>21.5</v>
+      </c>
+      <c r="M38">
+        <v>0.7559694</v>
+      </c>
+      <c r="N38">
+        <v>20.7440306</v>
+      </c>
+      <c r="O38">
+        <v>6.015768874</v>
+      </c>
+      <c r="P38">
+        <v>14.728261726</v>
+      </c>
+      <c r="Q38">
+        <v>15.028261726</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1856386447696744</v>
+      </c>
+      <c r="T38">
+        <v>0.7787125475057816</v>
+      </c>
+      <c r="U38">
+        <v>0.0457</v>
+      </c>
+      <c r="V38">
+        <v>0.29</v>
+      </c>
+      <c r="W38">
+        <v>0.032447</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>28.4403045943394</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1301218210394914</v>
+      </c>
+      <c r="C39">
+        <v>31.53158123467088</v>
+      </c>
+      <c r="D39">
+        <v>44.96308123467087</v>
+      </c>
+      <c r="E39">
+        <v>13.4515</v>
+      </c>
+      <c r="F39">
+        <v>17.0015</v>
+      </c>
+      <c r="G39">
+        <v>3.57</v>
+      </c>
+      <c r="H39">
+        <v>42.4</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>21.8</v>
+      </c>
+      <c r="K39">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L39">
+        <v>21.5</v>
+      </c>
+      <c r="M39">
+        <v>0.7769685499999999</v>
+      </c>
+      <c r="N39">
+        <v>20.72303145</v>
+      </c>
+      <c r="O39">
+        <v>6.009679120500001</v>
+      </c>
+      <c r="P39">
+        <v>14.7133523295</v>
+      </c>
+      <c r="Q39">
+        <v>15.0133523295</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1874863984753832</v>
+      </c>
+      <c r="T39">
+        <v>0.7885115278599842</v>
+      </c>
+      <c r="U39">
+        <v>0.0457</v>
+      </c>
+      <c r="V39">
+        <v>0.29</v>
+      </c>
+      <c r="W39">
+        <v>0.032447</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>27.67164771341131</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1297539894263913</v>
+      </c>
+      <c r="C40">
+        <v>31.13318683139589</v>
+      </c>
+      <c r="D40">
+        <v>45.02418683139589</v>
+      </c>
+      <c r="E40">
+        <v>13.911</v>
+      </c>
+      <c r="F40">
+        <v>17.461</v>
+      </c>
+      <c r="G40">
+        <v>3.57</v>
+      </c>
+      <c r="H40">
+        <v>42.4</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>21.8</v>
+      </c>
+      <c r="K40">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L40">
+        <v>21.5</v>
+      </c>
+      <c r="M40">
+        <v>0.7979677000000001</v>
+      </c>
+      <c r="N40">
+        <v>20.7020323</v>
+      </c>
+      <c r="O40">
+        <v>6.003589367000001</v>
+      </c>
+      <c r="P40">
+        <v>14.698442933</v>
+      </c>
+      <c r="Q40">
+        <v>14.998442933</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1893937571393407</v>
+      </c>
+      <c r="T40">
+        <v>0.7986266043546449</v>
+      </c>
+      <c r="U40">
+        <v>0.0457</v>
+      </c>
+      <c r="V40">
+        <v>0.29</v>
+      </c>
+      <c r="W40">
+        <v>0.032447</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>26.94344645779522</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1293861578132911</v>
+      </c>
+      <c r="C41">
+        <v>30.73495874124623</v>
+      </c>
+      <c r="D41">
+        <v>45.08545874124624</v>
+      </c>
+      <c r="E41">
+        <v>14.3705</v>
+      </c>
+      <c r="F41">
+        <v>17.9205</v>
+      </c>
+      <c r="G41">
+        <v>3.57</v>
+      </c>
+      <c r="H41">
+        <v>42.4</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>21.8</v>
+      </c>
+      <c r="K41">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L41">
+        <v>21.5</v>
+      </c>
+      <c r="M41">
+        <v>0.8189668500000001</v>
+      </c>
+      <c r="N41">
+        <v>20.68103315</v>
+      </c>
+      <c r="O41">
+        <v>5.997499613500001</v>
+      </c>
+      <c r="P41">
+        <v>14.6835335365</v>
+      </c>
+      <c r="Q41">
+        <v>14.9835335365</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1913636521529362</v>
+      </c>
+      <c r="T41">
+        <v>0.8090733227015897</v>
+      </c>
+      <c r="U41">
+        <v>0.0457</v>
+      </c>
+      <c r="V41">
+        <v>0.29</v>
+      </c>
+      <c r="W41">
+        <v>0.032447</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>26.25258885631329</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1290183262001909</v>
+      </c>
+      <c r="C42">
+        <v>30.33689764413711</v>
+      </c>
+      <c r="D42">
+        <v>45.14689764413711</v>
+      </c>
+      <c r="E42">
+        <v>14.83</v>
+      </c>
+      <c r="F42">
+        <v>18.38</v>
+      </c>
+      <c r="G42">
+        <v>3.57</v>
+      </c>
+      <c r="H42">
+        <v>42.4</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>21.8</v>
+      </c>
+      <c r="K42">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L42">
+        <v>21.5</v>
+      </c>
+      <c r="M42">
+        <v>0.839966</v>
+      </c>
+      <c r="N42">
+        <v>20.660034</v>
+      </c>
+      <c r="O42">
+        <v>5.991409860000001</v>
+      </c>
+      <c r="P42">
+        <v>14.66862414</v>
+      </c>
+      <c r="Q42">
+        <v>14.96862414</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1933992103336515</v>
+      </c>
+      <c r="T42">
+        <v>0.8198682649934327</v>
+      </c>
+      <c r="U42">
+        <v>0.0457</v>
+      </c>
+      <c r="V42">
+        <v>0.29</v>
+      </c>
+      <c r="W42">
+        <v>0.032447</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>25.59627413490546</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1286504945870907</v>
+      </c>
+      <c r="C43">
+        <v>29.93900422369487</v>
+      </c>
+      <c r="D43">
+        <v>45.20850422369487</v>
+      </c>
+      <c r="E43">
+        <v>15.2895</v>
+      </c>
+      <c r="F43">
+        <v>18.8395</v>
+      </c>
+      <c r="G43">
+        <v>3.57</v>
+      </c>
+      <c r="H43">
+        <v>42.4</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>21.8</v>
+      </c>
+      <c r="K43">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L43">
+        <v>21.5</v>
+      </c>
+      <c r="M43">
+        <v>0.8609651500000002</v>
+      </c>
+      <c r="N43">
+        <v>20.63903485</v>
+      </c>
+      <c r="O43">
+        <v>5.985320106500001</v>
+      </c>
+      <c r="P43">
+        <v>14.6537147435</v>
+      </c>
+      <c r="Q43">
+        <v>14.9537147435</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1955037704865945</v>
+      </c>
+      <c r="T43">
+        <v>0.8310291375324567</v>
+      </c>
+      <c r="U43">
+        <v>0.0457</v>
+      </c>
+      <c r="V43">
+        <v>0.29</v>
+      </c>
+      <c r="W43">
+        <v>0.032447</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>24.97197476576142</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1282826629739906</v>
+      </c>
+      <c r="C44">
+        <v>29.54127916728248</v>
+      </c>
+      <c r="D44">
+        <v>45.27027916728247</v>
+      </c>
+      <c r="E44">
+        <v>15.749</v>
+      </c>
+      <c r="F44">
+        <v>19.299</v>
+      </c>
+      <c r="G44">
+        <v>3.57</v>
+      </c>
+      <c r="H44">
+        <v>42.4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>21.8</v>
+      </c>
+      <c r="K44">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L44">
+        <v>21.5</v>
+      </c>
+      <c r="M44">
+        <v>0.8819642999999999</v>
+      </c>
+      <c r="N44">
+        <v>20.6180357</v>
+      </c>
+      <c r="O44">
+        <v>5.979230353000001</v>
+      </c>
+      <c r="P44">
+        <v>14.638805347</v>
+      </c>
+      <c r="Q44">
+        <v>14.938805347</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1976809016792941</v>
+      </c>
+      <c r="T44">
+        <v>0.8425748677452402</v>
+      </c>
+      <c r="U44">
+        <v>0.0457</v>
+      </c>
+      <c r="V44">
+        <v>0.29</v>
+      </c>
+      <c r="W44">
+        <v>0.032447</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>24.3774039380052</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1279148313608904</v>
+      </c>
+      <c r="C45">
+        <v>29.14372316602494</v>
+      </c>
+      <c r="D45">
+        <v>45.33222316602494</v>
+      </c>
+      <c r="E45">
+        <v>16.2085</v>
+      </c>
+      <c r="F45">
+        <v>19.7585</v>
+      </c>
+      <c r="G45">
+        <v>3.57</v>
+      </c>
+      <c r="H45">
+        <v>42.4</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>21.8</v>
+      </c>
+      <c r="K45">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L45">
+        <v>21.5</v>
+      </c>
+      <c r="M45">
+        <v>0.90296345</v>
+      </c>
+      <c r="N45">
+        <v>20.59703655</v>
+      </c>
+      <c r="O45">
+        <v>5.973140599500001</v>
+      </c>
+      <c r="P45">
+        <v>14.6238959505</v>
+      </c>
+      <c r="Q45">
+        <v>14.9238959505</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1999344234401585</v>
+      </c>
+      <c r="T45">
+        <v>0.8545257112988229</v>
+      </c>
+      <c r="U45">
+        <v>0.0457</v>
+      </c>
+      <c r="V45">
+        <v>0.29</v>
+      </c>
+      <c r="W45">
+        <v>0.032447</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>23.81048756735391</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1275469997477902</v>
+      </c>
+      <c r="C46">
+        <v>28.74633691483522</v>
+      </c>
+      <c r="D46">
+        <v>45.39433691483522</v>
+      </c>
+      <c r="E46">
+        <v>16.668</v>
+      </c>
+      <c r="F46">
+        <v>20.218</v>
+      </c>
+      <c r="G46">
+        <v>3.57</v>
+      </c>
+      <c r="H46">
+        <v>42.4</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>21.8</v>
+      </c>
+      <c r="K46">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L46">
+        <v>21.5</v>
+      </c>
+      <c r="M46">
+        <v>0.9239626000000001</v>
+      </c>
+      <c r="N46">
+        <v>20.5760374</v>
+      </c>
+      <c r="O46">
+        <v>5.967050846000001</v>
+      </c>
+      <c r="P46">
+        <v>14.608986554</v>
+      </c>
+      <c r="Q46">
+        <v>14.908986554</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2022684281210539</v>
+      </c>
+      <c r="T46">
+        <v>0.8669033706936053</v>
+      </c>
+      <c r="U46">
+        <v>0.0457</v>
+      </c>
+      <c r="V46">
+        <v>0.29</v>
+      </c>
+      <c r="W46">
+        <v>0.032447</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>23.26934012264133</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
         <v>0.45</v>
       </c>
-      <c r="V4">
-        <v>0.4368932038834951</v>
-      </c>
-      <c r="W4">
-        <v>0.07476340694006309</v>
-      </c>
-      <c r="X4">
-        <v>0.08046103689844347</v>
-      </c>
-      <c r="Y4">
-        <v>-0.005697629958380385</v>
-      </c>
-      <c r="Z4">
-        <v>0.0663815923437182</v>
-      </c>
-      <c r="AA4">
-        <v>0.02697255867431213</v>
-      </c>
-      <c r="AB4">
-        <v>0.08046103689844347</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05348847822413134</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>0</v>
-      </c>
-      <c r="AG4">
-        <v>-0.45</v>
-      </c>
-      <c r="AH4">
-        <v>0</v>
-      </c>
-      <c r="AI4">
-        <v>0</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.7758620689655171</v>
-      </c>
-      <c r="AK4">
-        <v>-0.0910931174089069</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>-0.011</v>
-      </c>
-      <c r="AN4">
-        <v>0</v>
-      </c>
-      <c r="AP4">
-        <v>-2.419354838709677</v>
-      </c>
-      <c r="AQ4">
-        <v>-16.81818181818182</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>TPL Properties Limited (KASE:TPLP)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Real Estate (Operations &amp; Services)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>-0.122</v>
-      </c>
-      <c r="E5">
-        <v>-0.308</v>
-      </c>
-      <c r="G5">
-        <v>-0.98159509202454</v>
-      </c>
-      <c r="H5">
-        <v>-0.98159509202454</v>
-      </c>
-      <c r="I5">
-        <v>-1.374233128834356</v>
-      </c>
-      <c r="J5">
-        <v>-1.374233128834356</v>
-      </c>
-      <c r="K5">
-        <v>0.291</v>
-      </c>
-      <c r="L5">
-        <v>0.1785276073619632</v>
-      </c>
-      <c r="M5">
-        <v>1.92</v>
-      </c>
-      <c r="N5">
-        <v>0.02640990371389271</v>
-      </c>
-      <c r="O5">
-        <v>6.597938144329897</v>
-      </c>
-      <c r="P5">
-        <v>1.92</v>
-      </c>
-      <c r="Q5">
-        <v>0.02640990371389271</v>
-      </c>
-      <c r="R5">
-        <v>6.597938144329897</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>20.9</v>
-      </c>
-      <c r="V5">
-        <v>0.2874828060522696</v>
-      </c>
-      <c r="W5">
-        <v>0.007617801047120417</v>
-      </c>
-      <c r="X5">
-        <v>0.09150408526465505</v>
-      </c>
-      <c r="Y5">
-        <v>-0.08388628421753463</v>
-      </c>
-      <c r="Z5">
-        <v>0.02966333030027297</v>
-      </c>
-      <c r="AA5">
-        <v>-0.04076433121019109</v>
-      </c>
-      <c r="AB5">
-        <v>0.08528477687977828</v>
-      </c>
-      <c r="AC5">
-        <v>-0.1260491080899694</v>
-      </c>
-      <c r="AD5">
-        <v>17.3</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>17.3</v>
-      </c>
-      <c r="AG5">
-        <v>-3.599999999999998</v>
-      </c>
-      <c r="AH5">
-        <v>0.1922222222222222</v>
-      </c>
-      <c r="AI5">
-        <v>0.3186003683241252</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.05209840810419678</v>
-      </c>
-      <c r="AK5">
-        <v>-0.1077844311377245</v>
-      </c>
-      <c r="AL5">
-        <v>2.11</v>
-      </c>
-      <c r="AM5">
-        <v>1.728</v>
-      </c>
-      <c r="AN5">
-        <v>-8.084112149532711</v>
-      </c>
-      <c r="AO5">
-        <v>-1.061611374407583</v>
-      </c>
-      <c r="AP5">
-        <v>1.682242990654204</v>
-      </c>
-      <c r="AQ5">
-        <v>-1.296296296296297</v>
+      <c r="B47">
+        <v>0.12717916813469</v>
+      </c>
+      <c r="C47">
+        <v>28.34912111244012</v>
+      </c>
+      <c r="D47">
+        <v>45.45662111244012</v>
+      </c>
+      <c r="E47">
+        <v>17.1275</v>
+      </c>
+      <c r="F47">
+        <v>20.6775</v>
+      </c>
+      <c r="G47">
+        <v>3.57</v>
+      </c>
+      <c r="H47">
+        <v>42.4</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>21.8</v>
+      </c>
+      <c r="K47">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L47">
+        <v>21.5</v>
+      </c>
+      <c r="M47">
+        <v>0.94496175</v>
+      </c>
+      <c r="N47">
+        <v>20.55503825</v>
+      </c>
+      <c r="O47">
+        <v>5.960961092500001</v>
+      </c>
+      <c r="P47">
+        <v>14.5940771575</v>
+      </c>
+      <c r="Q47">
+        <v>14.8940771575</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2046873056994364</v>
+      </c>
+      <c r="T47">
+        <v>0.8797311267936524</v>
+      </c>
+      <c r="U47">
+        <v>0.0457</v>
+      </c>
+      <c r="V47">
+        <v>0.29</v>
+      </c>
+      <c r="W47">
+        <v>0.032447</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>22.75224367547152</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1268113365215899</v>
+      </c>
+      <c r="C48">
+        <v>27.95207646140653</v>
+      </c>
+      <c r="D48">
+        <v>45.51907646140653</v>
+      </c>
+      <c r="E48">
+        <v>17.587</v>
+      </c>
+      <c r="F48">
+        <v>21.137</v>
+      </c>
+      <c r="G48">
+        <v>3.57</v>
+      </c>
+      <c r="H48">
+        <v>42.4</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>21.8</v>
+      </c>
+      <c r="K48">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L48">
+        <v>21.5</v>
+      </c>
+      <c r="M48">
+        <v>0.9659609000000001</v>
+      </c>
+      <c r="N48">
+        <v>20.5340391</v>
+      </c>
+      <c r="O48">
+        <v>5.954871339000001</v>
+      </c>
+      <c r="P48">
+        <v>14.579167761</v>
+      </c>
+      <c r="Q48">
+        <v>14.879167761</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2071957713362775</v>
+      </c>
+      <c r="T48">
+        <v>0.8930339849714791</v>
+      </c>
+      <c r="U48">
+        <v>0.0457</v>
+      </c>
+      <c r="V48">
+        <v>0.29</v>
+      </c>
+      <c r="W48">
+        <v>0.032447</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>22.25762968252648</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1264435049084897</v>
+      </c>
+      <c r="C49">
+        <v>27.55520366816783</v>
+      </c>
+      <c r="D49">
+        <v>45.58170366816783</v>
+      </c>
+      <c r="E49">
+        <v>18.0465</v>
+      </c>
+      <c r="F49">
+        <v>21.5965</v>
+      </c>
+      <c r="G49">
+        <v>3.57</v>
+      </c>
+      <c r="H49">
+        <v>42.4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>21.8</v>
+      </c>
+      <c r="K49">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L49">
+        <v>21.5</v>
+      </c>
+      <c r="M49">
+        <v>0.9869600500000001</v>
+      </c>
+      <c r="N49">
+        <v>20.51303995</v>
+      </c>
+      <c r="O49">
+        <v>5.948781585500001</v>
+      </c>
+      <c r="P49">
+        <v>14.5642583645</v>
+      </c>
+      <c r="Q49">
+        <v>14.8642583645</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2097988960537541</v>
+      </c>
+      <c r="T49">
+        <v>0.9068388377975255</v>
+      </c>
+      <c r="U49">
+        <v>0.0457</v>
+      </c>
+      <c r="V49">
+        <v>0.29</v>
+      </c>
+      <c r="W49">
+        <v>0.032447</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>21.78406309353656</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1260756732953895</v>
+      </c>
+      <c r="C50">
+        <v>27.15850344305054</v>
+      </c>
+      <c r="D50">
+        <v>45.64450344305054</v>
+      </c>
+      <c r="E50">
+        <v>18.506</v>
+      </c>
+      <c r="F50">
+        <v>22.056</v>
+      </c>
+      <c r="G50">
+        <v>3.57</v>
+      </c>
+      <c r="H50">
+        <v>42.4</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>21.8</v>
+      </c>
+      <c r="K50">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L50">
+        <v>21.5</v>
+      </c>
+      <c r="M50">
+        <v>1.0079592</v>
+      </c>
+      <c r="N50">
+        <v>20.4920408</v>
+      </c>
+      <c r="O50">
+        <v>5.942691832000001</v>
+      </c>
+      <c r="P50">
+        <v>14.549348968</v>
+      </c>
+      <c r="Q50">
+        <v>14.849348968</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2125021409526721</v>
+      </c>
+      <c r="T50">
+        <v>0.9211746465014969</v>
+      </c>
+      <c r="U50">
+        <v>0.0457</v>
+      </c>
+      <c r="V50">
+        <v>0.29</v>
+      </c>
+      <c r="W50">
+        <v>0.032447</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>21.33022844575455</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1257078416822894</v>
+      </c>
+      <c r="C51">
+        <v>26.76197650030113</v>
+      </c>
+      <c r="D51">
+        <v>45.70747650030113</v>
+      </c>
+      <c r="E51">
+        <v>18.9655</v>
+      </c>
+      <c r="F51">
+        <v>22.5155</v>
+      </c>
+      <c r="G51">
+        <v>3.57</v>
+      </c>
+      <c r="H51">
+        <v>42.4</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>21.8</v>
+      </c>
+      <c r="K51">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L51">
+        <v>21.5</v>
+      </c>
+      <c r="M51">
+        <v>1.02895835</v>
+      </c>
+      <c r="N51">
+        <v>20.47104165</v>
+      </c>
+      <c r="O51">
+        <v>5.936602078500001</v>
+      </c>
+      <c r="P51">
+        <v>14.5344395715</v>
+      </c>
+      <c r="Q51">
+        <v>14.8344395715</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2153113954554693</v>
+      </c>
+      <c r="T51">
+        <v>0.9360726437820945</v>
+      </c>
+      <c r="U51">
+        <v>0.0457</v>
+      </c>
+      <c r="V51">
+        <v>0.29</v>
+      </c>
+      <c r="W51">
+        <v>0.032447</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>20.89491766114732</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1253400100691892</v>
+      </c>
+      <c r="C52">
+        <v>26.36562355811318</v>
+      </c>
+      <c r="D52">
+        <v>45.77062355811318</v>
+      </c>
+      <c r="E52">
+        <v>19.425</v>
+      </c>
+      <c r="F52">
+        <v>22.975</v>
+      </c>
+      <c r="G52">
+        <v>3.57</v>
+      </c>
+      <c r="H52">
+        <v>42.4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>21.8</v>
+      </c>
+      <c r="K52">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L52">
+        <v>21.5</v>
+      </c>
+      <c r="M52">
+        <v>1.0499575</v>
+      </c>
+      <c r="N52">
+        <v>20.4500425</v>
+      </c>
+      <c r="O52">
+        <v>5.930512325</v>
+      </c>
+      <c r="P52">
+        <v>14.519530175</v>
+      </c>
+      <c r="Q52">
+        <v>14.819530175</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2182330201383783</v>
+      </c>
+      <c r="T52">
+        <v>0.9515665609539161</v>
+      </c>
+      <c r="U52">
+        <v>0.0457</v>
+      </c>
+      <c r="V52">
+        <v>0.29</v>
+      </c>
+      <c r="W52">
+        <v>0.032447</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>20.47701930792437</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.124972178456089</v>
+      </c>
+      <c r="C53">
+        <v>25.96944533865461</v>
+      </c>
+      <c r="D53">
+        <v>45.83394533865461</v>
+      </c>
+      <c r="E53">
+        <v>19.8845</v>
+      </c>
+      <c r="F53">
+        <v>23.4345</v>
+      </c>
+      <c r="G53">
+        <v>3.57</v>
+      </c>
+      <c r="H53">
+        <v>42.4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>21.8</v>
+      </c>
+      <c r="K53">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L53">
+        <v>21.5</v>
+      </c>
+      <c r="M53">
+        <v>1.07095665</v>
+      </c>
+      <c r="N53">
+        <v>20.42904335</v>
+      </c>
+      <c r="O53">
+        <v>5.924422571500001</v>
+      </c>
+      <c r="P53">
+        <v>14.5046207785</v>
+      </c>
+      <c r="Q53">
+        <v>14.8046207785</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2212738948083449</v>
+      </c>
+      <c r="T53">
+        <v>0.9676928829082612</v>
+      </c>
+      <c r="U53">
+        <v>0.0457</v>
+      </c>
+      <c r="V53">
+        <v>0.29</v>
+      </c>
+      <c r="W53">
+        <v>0.032447</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>20.07550912541605</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1246043468429888</v>
+      </c>
+      <c r="C54">
+        <v>25.57344256809522</v>
+      </c>
+      <c r="D54">
+        <v>45.89744256809522</v>
+      </c>
+      <c r="E54">
+        <v>20.344</v>
+      </c>
+      <c r="F54">
+        <v>23.894</v>
+      </c>
+      <c r="G54">
+        <v>3.57</v>
+      </c>
+      <c r="H54">
+        <v>42.4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>21.8</v>
+      </c>
+      <c r="K54">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L54">
+        <v>21.5</v>
+      </c>
+      <c r="M54">
+        <v>1.0919558</v>
+      </c>
+      <c r="N54">
+        <v>20.4080442</v>
+      </c>
+      <c r="O54">
+        <v>5.918332818000001</v>
+      </c>
+      <c r="P54">
+        <v>14.489711382</v>
+      </c>
+      <c r="Q54">
+        <v>14.789711382</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.22444147258956</v>
+      </c>
+      <c r="T54">
+        <v>0.9844911349440371</v>
+      </c>
+      <c r="U54">
+        <v>0.0457</v>
+      </c>
+      <c r="V54">
+        <v>0.29</v>
+      </c>
+      <c r="W54">
+        <v>0.032447</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>19.68944164223497</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1242365152298886</v>
+      </c>
+      <c r="C55">
+        <v>25.1776159766345</v>
+      </c>
+      <c r="D55">
+        <v>45.9611159766345</v>
+      </c>
+      <c r="E55">
+        <v>20.8035</v>
+      </c>
+      <c r="F55">
+        <v>24.3535</v>
+      </c>
+      <c r="G55">
+        <v>3.57</v>
+      </c>
+      <c r="H55">
+        <v>42.4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>21.8</v>
+      </c>
+      <c r="K55">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L55">
+        <v>21.5</v>
+      </c>
+      <c r="M55">
+        <v>1.11295495</v>
+      </c>
+      <c r="N55">
+        <v>20.38704505</v>
+      </c>
+      <c r="O55">
+        <v>5.912243064500001</v>
+      </c>
+      <c r="P55">
+        <v>14.4748019855</v>
+      </c>
+      <c r="Q55">
+        <v>14.7748019855</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2277438409146567</v>
+      </c>
+      <c r="T55">
+        <v>1.002004206215378</v>
+      </c>
+      <c r="U55">
+        <v>0.0457</v>
+      </c>
+      <c r="V55">
+        <v>0.29</v>
+      </c>
+      <c r="W55">
+        <v>0.032447</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>19.31794274332487</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1238686836167885</v>
+      </c>
+      <c r="C56">
+        <v>24.78196629852956</v>
+      </c>
+      <c r="D56">
+        <v>46.02496629852956</v>
+      </c>
+      <c r="E56">
+        <v>21.263</v>
+      </c>
+      <c r="F56">
+        <v>24.813</v>
+      </c>
+      <c r="G56">
+        <v>3.57</v>
+      </c>
+      <c r="H56">
+        <v>42.4</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>21.8</v>
+      </c>
+      <c r="K56">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L56">
+        <v>21.5</v>
+      </c>
+      <c r="M56">
+        <v>1.1339541</v>
+      </c>
+      <c r="N56">
+        <v>20.3660459</v>
+      </c>
+      <c r="O56">
+        <v>5.906153311000001</v>
+      </c>
+      <c r="P56">
+        <v>14.459892589</v>
+      </c>
+      <c r="Q56">
+        <v>14.759892589</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2311897904712793</v>
+      </c>
+      <c r="T56">
+        <v>1.020278715368081</v>
+      </c>
+      <c r="U56">
+        <v>0.0457</v>
+      </c>
+      <c r="V56">
+        <v>0.29</v>
+      </c>
+      <c r="W56">
+        <v>0.032447</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>18.96020306289293</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1235008520036883</v>
+      </c>
+      <c r="C57">
+        <v>24.38649427212337</v>
+      </c>
+      <c r="D57">
+        <v>46.08899427212337</v>
+      </c>
+      <c r="E57">
+        <v>21.7225</v>
+      </c>
+      <c r="F57">
+        <v>25.2725</v>
+      </c>
+      <c r="G57">
+        <v>3.57</v>
+      </c>
+      <c r="H57">
+        <v>42.4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>21.8</v>
+      </c>
+      <c r="K57">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L57">
+        <v>21.5</v>
+      </c>
+      <c r="M57">
+        <v>1.15495325</v>
+      </c>
+      <c r="N57">
+        <v>20.34504675</v>
+      </c>
+      <c r="O57">
+        <v>5.900063557500001</v>
+      </c>
+      <c r="P57">
+        <v>14.4449831925</v>
+      </c>
+      <c r="Q57">
+        <v>14.7449831925</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2347888933415296</v>
+      </c>
+      <c r="T57">
+        <v>1.039365424927572</v>
+      </c>
+      <c r="U57">
+        <v>0.0457</v>
+      </c>
+      <c r="V57">
+        <v>0.29</v>
+      </c>
+      <c r="W57">
+        <v>0.032447</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>18.61547209811306</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1231330203905881</v>
+      </c>
+      <c r="C58">
+        <v>23.99120063987328</v>
+      </c>
+      <c r="D58">
+        <v>46.15320063987328</v>
+      </c>
+      <c r="E58">
+        <v>22.182</v>
+      </c>
+      <c r="F58">
+        <v>25.732</v>
+      </c>
+      <c r="G58">
+        <v>3.57</v>
+      </c>
+      <c r="H58">
+        <v>42.4</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>21.8</v>
+      </c>
+      <c r="K58">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L58">
+        <v>21.5</v>
+      </c>
+      <c r="M58">
+        <v>1.1759524</v>
+      </c>
+      <c r="N58">
+        <v>20.3240476</v>
+      </c>
+      <c r="O58">
+        <v>5.893973804000001</v>
+      </c>
+      <c r="P58">
+        <v>14.430073796</v>
+      </c>
+      <c r="Q58">
+        <v>14.730073796</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2385515917967912</v>
+      </c>
+      <c r="T58">
+        <v>1.059319712194312</v>
+      </c>
+      <c r="U58">
+        <v>0.0457</v>
+      </c>
+      <c r="V58">
+        <v>0.29</v>
+      </c>
+      <c r="W58">
+        <v>0.032447</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>18.2830529535039</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1227651887774879</v>
+      </c>
+      <c r="C59">
+        <v>23.59608614837959</v>
+      </c>
+      <c r="D59">
+        <v>46.2175861483796</v>
+      </c>
+      <c r="E59">
+        <v>22.6415</v>
+      </c>
+      <c r="F59">
+        <v>26.1915</v>
+      </c>
+      <c r="G59">
+        <v>3.57</v>
+      </c>
+      <c r="H59">
+        <v>42.4</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>21.8</v>
+      </c>
+      <c r="K59">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L59">
+        <v>21.5</v>
+      </c>
+      <c r="M59">
+        <v>1.19695155</v>
+      </c>
+      <c r="N59">
+        <v>20.30304845</v>
+      </c>
+      <c r="O59">
+        <v>5.8878840505</v>
+      </c>
+      <c r="P59">
+        <v>14.4151643995</v>
+      </c>
+      <c r="Q59">
+        <v>14.7151643995</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2424892994825301</v>
+      </c>
+      <c r="T59">
+        <v>1.080202105845551</v>
+      </c>
+      <c r="U59">
+        <v>0.0457</v>
+      </c>
+      <c r="V59">
+        <v>0.29</v>
+      </c>
+      <c r="W59">
+        <v>0.032447</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>17.96229763853015</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1223973571643878</v>
+      </c>
+      <c r="C60">
+        <v>23.20115154841465</v>
+      </c>
+      <c r="D60">
+        <v>46.28215154841465</v>
+      </c>
+      <c r="E60">
+        <v>23.101</v>
+      </c>
+      <c r="F60">
+        <v>26.651</v>
+      </c>
+      <c r="G60">
+        <v>3.57</v>
+      </c>
+      <c r="H60">
+        <v>42.4</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>21.8</v>
+      </c>
+      <c r="K60">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L60">
+        <v>21.5</v>
+      </c>
+      <c r="M60">
+        <v>1.2179507</v>
+      </c>
+      <c r="N60">
+        <v>20.2820493</v>
+      </c>
+      <c r="O60">
+        <v>5.881794297000001</v>
+      </c>
+      <c r="P60">
+        <v>14.400255003</v>
+      </c>
+      <c r="Q60">
+        <v>14.700255003</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2466145170580661</v>
+      </c>
+      <c r="T60">
+        <v>1.102078899194469</v>
+      </c>
+      <c r="U60">
+        <v>0.0457</v>
+      </c>
+      <c r="V60">
+        <v>0.29</v>
+      </c>
+      <c r="W60">
+        <v>0.032447</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>17.65260285165894</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1220295255512876</v>
+      </c>
+      <c r="C61">
+        <v>22.80639759495187</v>
+      </c>
+      <c r="D61">
+        <v>46.34689759495187</v>
+      </c>
+      <c r="E61">
+        <v>23.56049999999999</v>
+      </c>
+      <c r="F61">
+        <v>27.11049999999999</v>
+      </c>
+      <c r="G61">
+        <v>3.57</v>
+      </c>
+      <c r="H61">
+        <v>42.4</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>21.8</v>
+      </c>
+      <c r="K61">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L61">
+        <v>21.5</v>
+      </c>
+      <c r="M61">
+        <v>1.23894985</v>
+      </c>
+      <c r="N61">
+        <v>20.26105015</v>
+      </c>
+      <c r="O61">
+        <v>5.8757045435</v>
+      </c>
+      <c r="P61">
+        <v>14.3853456065</v>
+      </c>
+      <c r="Q61">
+        <v>14.6853456065</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.250940964759238</v>
+      </c>
+      <c r="T61">
+        <v>1.125022853194553</v>
+      </c>
+      <c r="U61">
+        <v>0.0457</v>
+      </c>
+      <c r="V61">
+        <v>0.29</v>
+      </c>
+      <c r="W61">
+        <v>0.032447</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>17.35340619315625</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1216616939381874</v>
+      </c>
+      <c r="C62">
+        <v>22.41182504719532</v>
+      </c>
+      <c r="D62">
+        <v>46.41182504719531</v>
+      </c>
+      <c r="E62">
+        <v>24.02</v>
+      </c>
+      <c r="F62">
+        <v>27.57</v>
+      </c>
+      <c r="G62">
+        <v>3.57</v>
+      </c>
+      <c r="H62">
+        <v>42.4</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>21.8</v>
+      </c>
+      <c r="K62">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L62">
+        <v>21.5</v>
+      </c>
+      <c r="M62">
+        <v>1.259949</v>
+      </c>
+      <c r="N62">
+        <v>20.240051</v>
+      </c>
+      <c r="O62">
+        <v>5.869614790000001</v>
+      </c>
+      <c r="P62">
+        <v>14.37043621</v>
+      </c>
+      <c r="Q62">
+        <v>14.67043621</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2554837348454685</v>
+      </c>
+      <c r="T62">
+        <v>1.149114004894641</v>
+      </c>
+      <c r="U62">
+        <v>0.0457</v>
+      </c>
+      <c r="V62">
+        <v>0.29</v>
+      </c>
+      <c r="W62">
+        <v>0.032447</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>17.06418275660364</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1212938623250872</v>
+      </c>
+      <c r="C63">
+        <v>22.01743466860926</v>
+      </c>
+      <c r="D63">
+        <v>46.47693466860925</v>
+      </c>
+      <c r="E63">
+        <v>24.47949999999999</v>
+      </c>
+      <c r="F63">
+        <v>28.0295</v>
+      </c>
+      <c r="G63">
+        <v>3.57</v>
+      </c>
+      <c r="H63">
+        <v>42.4</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>21.8</v>
+      </c>
+      <c r="K63">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L63">
+        <v>21.5</v>
+      </c>
+      <c r="M63">
+        <v>1.28094815</v>
+      </c>
+      <c r="N63">
+        <v>20.21905185</v>
+      </c>
+      <c r="O63">
+        <v>5.8635250365</v>
+      </c>
+      <c r="P63">
+        <v>14.3555268135</v>
+      </c>
+      <c r="Q63">
+        <v>14.6555268135</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2602594675002237</v>
+      </c>
+      <c r="T63">
+        <v>1.174440600271657</v>
+      </c>
+      <c r="U63">
+        <v>0.0457</v>
+      </c>
+      <c r="V63">
+        <v>0.29</v>
+      </c>
+      <c r="W63">
+        <v>0.032447</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>16.78444205567571</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1209260307119871</v>
+      </c>
+      <c r="C64">
+        <v>21.62322722694813</v>
+      </c>
+      <c r="D64">
+        <v>46.54222722694813</v>
+      </c>
+      <c r="E64">
+        <v>24.939</v>
+      </c>
+      <c r="F64">
+        <v>28.489</v>
+      </c>
+      <c r="G64">
+        <v>3.57</v>
+      </c>
+      <c r="H64">
+        <v>42.4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>21.8</v>
+      </c>
+      <c r="K64">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L64">
+        <v>21.5</v>
+      </c>
+      <c r="M64">
+        <v>1.3019473</v>
+      </c>
+      <c r="N64">
+        <v>20.1980527</v>
+      </c>
+      <c r="O64">
+        <v>5.857435283000001</v>
+      </c>
+      <c r="P64">
+        <v>14.340617417</v>
+      </c>
+      <c r="Q64">
+        <v>14.640617417</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2652865545052291</v>
+      </c>
+      <c r="T64">
+        <v>1.201100174352727</v>
+      </c>
+      <c r="U64">
+        <v>0.0457</v>
+      </c>
+      <c r="V64">
+        <v>0.29</v>
+      </c>
+      <c r="W64">
+        <v>0.032447</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>16.5137252483261</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1205581990988869</v>
+      </c>
+      <c r="C65">
+        <v>21.22920349428677</v>
+      </c>
+      <c r="D65">
+        <v>46.60770349428677</v>
+      </c>
+      <c r="E65">
+        <v>25.3985</v>
+      </c>
+      <c r="F65">
+        <v>28.9485</v>
+      </c>
+      <c r="G65">
+        <v>3.57</v>
+      </c>
+      <c r="H65">
+        <v>42.4</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>21.8</v>
+      </c>
+      <c r="K65">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L65">
+        <v>21.5</v>
+      </c>
+      <c r="M65">
+        <v>1.32294645</v>
+      </c>
+      <c r="N65">
+        <v>20.17705355</v>
+      </c>
+      <c r="O65">
+        <v>5.851345529500001</v>
+      </c>
+      <c r="P65">
+        <v>14.3257080205</v>
+      </c>
+      <c r="Q65">
+        <v>14.6257080205</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2705853759429376</v>
+      </c>
+      <c r="T65">
+        <v>1.229200806492233</v>
+      </c>
+      <c r="U65">
+        <v>0.0457</v>
+      </c>
+      <c r="V65">
+        <v>0.29</v>
+      </c>
+      <c r="W65">
+        <v>0.032447</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>16.2516026253368</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1201903674857868</v>
+      </c>
+      <c r="C66">
+        <v>20.83536424705074</v>
+      </c>
+      <c r="D66">
+        <v>46.67336424705074</v>
+      </c>
+      <c r="E66">
+        <v>25.858</v>
+      </c>
+      <c r="F66">
+        <v>29.408</v>
+      </c>
+      <c r="G66">
+        <v>3.57</v>
+      </c>
+      <c r="H66">
+        <v>42.4</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>21.8</v>
+      </c>
+      <c r="K66">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L66">
+        <v>21.5</v>
+      </c>
+      <c r="M66">
+        <v>1.3439456</v>
+      </c>
+      <c r="N66">
+        <v>20.1560544</v>
+      </c>
+      <c r="O66">
+        <v>5.845255776</v>
+      </c>
+      <c r="P66">
+        <v>14.310798624</v>
+      </c>
+      <c r="Q66">
+        <v>14.610798624</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2761785763494076</v>
+      </c>
+      <c r="T66">
+        <v>1.258862584861711</v>
+      </c>
+      <c r="U66">
+        <v>0.0457</v>
+      </c>
+      <c r="V66">
+        <v>0.29</v>
+      </c>
+      <c r="W66">
+        <v>0.032447</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>15.99767133431591</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1198225358726866</v>
+      </c>
+      <c r="C67">
+        <v>20.44171026604711</v>
+      </c>
+      <c r="D67">
+        <v>46.73921026604711</v>
+      </c>
+      <c r="E67">
+        <v>26.3175</v>
+      </c>
+      <c r="F67">
+        <v>29.8675</v>
+      </c>
+      <c r="G67">
+        <v>3.57</v>
+      </c>
+      <c r="H67">
+        <v>42.4</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>21.8</v>
+      </c>
+      <c r="K67">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L67">
+        <v>21.5</v>
+      </c>
+      <c r="M67">
+        <v>1.36494475</v>
+      </c>
+      <c r="N67">
+        <v>20.13505525</v>
+      </c>
+      <c r="O67">
+        <v>5.839166022500001</v>
+      </c>
+      <c r="P67">
+        <v>14.2958892275</v>
+      </c>
+      <c r="Q67">
+        <v>14.5958892275</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2820913882076759</v>
+      </c>
+      <c r="T67">
+        <v>1.290219321995159</v>
+      </c>
+      <c r="U67">
+        <v>0.0457</v>
+      </c>
+      <c r="V67">
+        <v>0.29</v>
+      </c>
+      <c r="W67">
+        <v>0.032447</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>15.75155331378798</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1194547042595864</v>
+      </c>
+      <c r="C68">
+        <v>20.04824233649538</v>
+      </c>
+      <c r="D68">
+        <v>46.80524233649538</v>
+      </c>
+      <c r="E68">
+        <v>26.777</v>
+      </c>
+      <c r="F68">
+        <v>30.327</v>
+      </c>
+      <c r="G68">
+        <v>3.57</v>
+      </c>
+      <c r="H68">
+        <v>42.4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>21.8</v>
+      </c>
+      <c r="K68">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L68">
+        <v>21.5</v>
+      </c>
+      <c r="M68">
+        <v>1.3859439</v>
+      </c>
+      <c r="N68">
+        <v>20.1140561</v>
+      </c>
+      <c r="O68">
+        <v>5.833076269</v>
+      </c>
+      <c r="P68">
+        <v>14.280979831</v>
+      </c>
+      <c r="Q68">
+        <v>14.580979831</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2883520125281953</v>
+      </c>
+      <c r="T68">
+        <v>1.323420573077634</v>
+      </c>
+      <c r="U68">
+        <v>0.0457</v>
+      </c>
+      <c r="V68">
+        <v>0.29</v>
+      </c>
+      <c r="W68">
+        <v>0.032447</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>15.51289341509422</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1190868726464862</v>
+      </c>
+      <c r="C69">
+        <v>19.65496124805867</v>
+      </c>
+      <c r="D69">
+        <v>46.87146124805867</v>
+      </c>
+      <c r="E69">
+        <v>27.2365</v>
+      </c>
+      <c r="F69">
+        <v>30.7865</v>
+      </c>
+      <c r="G69">
+        <v>3.57</v>
+      </c>
+      <c r="H69">
+        <v>42.4</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>21.8</v>
+      </c>
+      <c r="K69">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L69">
+        <v>21.5</v>
+      </c>
+      <c r="M69">
+        <v>1.40694305</v>
+      </c>
+      <c r="N69">
+        <v>20.09305695</v>
+      </c>
+      <c r="O69">
+        <v>5.826986515500001</v>
+      </c>
+      <c r="P69">
+        <v>14.2660704345</v>
+      </c>
+      <c r="Q69">
+        <v>14.5660704345</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2949920686257158</v>
+      </c>
+      <c r="T69">
+        <v>1.358634021195411</v>
+      </c>
+      <c r="U69">
+        <v>0.0457</v>
+      </c>
+      <c r="V69">
+        <v>0.29</v>
+      </c>
+      <c r="W69">
+        <v>0.032447</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>15.28135769248087</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.118719041033386</v>
+      </c>
+      <c r="C70">
+        <v>19.2618677948752</v>
+      </c>
+      <c r="D70">
+        <v>46.9378677948752</v>
+      </c>
+      <c r="E70">
+        <v>27.696</v>
+      </c>
+      <c r="F70">
+        <v>31.246</v>
+      </c>
+      <c r="G70">
+        <v>3.57</v>
+      </c>
+      <c r="H70">
+        <v>42.4</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>21.8</v>
+      </c>
+      <c r="K70">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L70">
+        <v>21.5</v>
+      </c>
+      <c r="M70">
+        <v>1.4279422</v>
+      </c>
+      <c r="N70">
+        <v>20.0720578</v>
+      </c>
+      <c r="O70">
+        <v>5.820896762</v>
+      </c>
+      <c r="P70">
+        <v>14.251161038</v>
+      </c>
+      <c r="Q70">
+        <v>14.551161038</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.3020471282293314</v>
+      </c>
+      <c r="T70">
+        <v>1.396048309820548</v>
+      </c>
+      <c r="U70">
+        <v>0.0457</v>
+      </c>
+      <c r="V70">
+        <v>0.29</v>
+      </c>
+      <c r="W70">
+        <v>0.032447</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>15.05663184406203</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1183512094202859</v>
+      </c>
+      <c r="C71">
+        <v>18.86896277559009</v>
+      </c>
+      <c r="D71">
+        <v>47.00446277559009</v>
+      </c>
+      <c r="E71">
+        <v>28.1555</v>
+      </c>
+      <c r="F71">
+        <v>31.7055</v>
+      </c>
+      <c r="G71">
+        <v>3.57</v>
+      </c>
+      <c r="H71">
+        <v>42.4</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>21.8</v>
+      </c>
+      <c r="K71">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L71">
+        <v>21.5</v>
+      </c>
+      <c r="M71">
+        <v>1.44894135</v>
+      </c>
+      <c r="N71">
+        <v>20.05105865</v>
+      </c>
+      <c r="O71">
+        <v>5.814807008500001</v>
+      </c>
+      <c r="P71">
+        <v>14.2362516415</v>
+      </c>
+      <c r="Q71">
+        <v>14.5362516415</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3095573529686642</v>
+      </c>
+      <c r="T71">
+        <v>1.435876423518275</v>
+      </c>
+      <c r="U71">
+        <v>0.0457</v>
+      </c>
+      <c r="V71">
+        <v>0.29</v>
+      </c>
+      <c r="W71">
+        <v>0.032447</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>14.83841978835099</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1179833778071857</v>
+      </c>
+      <c r="C72">
+        <v>18.47624699338733</v>
+      </c>
+      <c r="D72">
+        <v>47.07124699338733</v>
+      </c>
+      <c r="E72">
+        <v>28.615</v>
+      </c>
+      <c r="F72">
+        <v>32.165</v>
+      </c>
+      <c r="G72">
+        <v>3.57</v>
+      </c>
+      <c r="H72">
+        <v>42.4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>21.8</v>
+      </c>
+      <c r="K72">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L72">
+        <v>21.5</v>
+      </c>
+      <c r="M72">
+        <v>1.4699405</v>
+      </c>
+      <c r="N72">
+        <v>20.0300595</v>
+      </c>
+      <c r="O72">
+        <v>5.808717255</v>
+      </c>
+      <c r="P72">
+        <v>14.221342245</v>
+      </c>
+      <c r="Q72">
+        <v>14.521342245</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3175682593572857</v>
+      </c>
+      <c r="T72">
+        <v>1.478359744795851</v>
+      </c>
+      <c r="U72">
+        <v>0.0457</v>
+      </c>
+      <c r="V72">
+        <v>0.29</v>
+      </c>
+      <c r="W72">
+        <v>0.032447</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>14.62644236280312</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1176155461940855</v>
+      </c>
+      <c r="C73">
+        <v>18.08372125602205</v>
+      </c>
+      <c r="D73">
+        <v>47.13822125602204</v>
+      </c>
+      <c r="E73">
+        <v>29.0745</v>
+      </c>
+      <c r="F73">
+        <v>32.6245</v>
+      </c>
+      <c r="G73">
+        <v>3.57</v>
+      </c>
+      <c r="H73">
+        <v>42.4</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>21.8</v>
+      </c>
+      <c r="K73">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L73">
+        <v>21.5</v>
+      </c>
+      <c r="M73">
+        <v>1.49093965</v>
+      </c>
+      <c r="N73">
+        <v>20.00906035</v>
+      </c>
+      <c r="O73">
+        <v>5.8026275015</v>
+      </c>
+      <c r="P73">
+        <v>14.2064328485</v>
+      </c>
+      <c r="Q73">
+        <v>14.5064328485</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3261316420485708</v>
+      </c>
+      <c r="T73">
+        <v>1.523772950299465</v>
+      </c>
+      <c r="U73">
+        <v>0.0457</v>
+      </c>
+      <c r="V73">
+        <v>0.29</v>
+      </c>
+      <c r="W73">
+        <v>0.032447</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>14.4204361323411</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1172477145809853</v>
+      </c>
+      <c r="C74">
+        <v>17.69138637585314</v>
+      </c>
+      <c r="D74">
+        <v>47.20538637585314</v>
+      </c>
+      <c r="E74">
+        <v>29.534</v>
+      </c>
+      <c r="F74">
+        <v>33.084</v>
+      </c>
+      <c r="G74">
+        <v>3.57</v>
+      </c>
+      <c r="H74">
+        <v>42.4</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>21.8</v>
+      </c>
+      <c r="K74">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L74">
+        <v>21.5</v>
+      </c>
+      <c r="M74">
+        <v>1.5119388</v>
+      </c>
+      <c r="N74">
+        <v>19.9880612</v>
+      </c>
+      <c r="O74">
+        <v>5.796537748000001</v>
+      </c>
+      <c r="P74">
+        <v>14.191523452</v>
+      </c>
+      <c r="Q74">
+        <v>14.491523452</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3353066949320905</v>
+      </c>
+      <c r="T74">
+        <v>1.572429956196196</v>
+      </c>
+      <c r="U74">
+        <v>0.0457</v>
+      </c>
+      <c r="V74">
+        <v>0.29</v>
+      </c>
+      <c r="W74">
+        <v>0.032447</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>14.2201522971697</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1168798829678852</v>
+      </c>
+      <c r="C75">
+        <v>17.29924316987608</v>
+      </c>
+      <c r="D75">
+        <v>47.27274316987607</v>
+      </c>
+      <c r="E75">
+        <v>29.99349999999999</v>
+      </c>
+      <c r="F75">
+        <v>33.54349999999999</v>
+      </c>
+      <c r="G75">
+        <v>3.57</v>
+      </c>
+      <c r="H75">
+        <v>42.4</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>21.8</v>
+      </c>
+      <c r="K75">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L75">
+        <v>21.5</v>
+      </c>
+      <c r="M75">
+        <v>1.53293795</v>
+      </c>
+      <c r="N75">
+        <v>19.96706205</v>
+      </c>
+      <c r="O75">
+        <v>5.7904479945</v>
+      </c>
+      <c r="P75">
+        <v>14.1766140555</v>
+      </c>
+      <c r="Q75">
+        <v>14.4766140555</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3451613813625376</v>
+      </c>
+      <c r="T75">
+        <v>1.624691184751943</v>
+      </c>
+      <c r="U75">
+        <v>0.0457</v>
+      </c>
+      <c r="V75">
+        <v>0.29</v>
+      </c>
+      <c r="W75">
+        <v>0.032447</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>14.02535569035916</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.116512051354785</v>
+      </c>
+      <c r="C76">
+        <v>16.90729245975602</v>
+      </c>
+      <c r="D76">
+        <v>47.34029245975601</v>
+      </c>
+      <c r="E76">
+        <v>30.45299999999999</v>
+      </c>
+      <c r="F76">
+        <v>34.00299999999999</v>
+      </c>
+      <c r="G76">
+        <v>3.57</v>
+      </c>
+      <c r="H76">
+        <v>42.4</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>21.8</v>
+      </c>
+      <c r="K76">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L76">
+        <v>21.5</v>
+      </c>
+      <c r="M76">
+        <v>1.5539371</v>
+      </c>
+      <c r="N76">
+        <v>19.9460629</v>
+      </c>
+      <c r="O76">
+        <v>5.784358241000001</v>
+      </c>
+      <c r="P76">
+        <v>14.161704659</v>
+      </c>
+      <c r="Q76">
+        <v>14.461704659</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3557741205953269</v>
+      </c>
+      <c r="T76">
+        <v>1.680972507811979</v>
+      </c>
+      <c r="U76">
+        <v>0.0457</v>
+      </c>
+      <c r="V76">
+        <v>0.29</v>
+      </c>
+      <c r="W76">
+        <v>0.032447</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>13.83582385670566</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1161442197416848</v>
+      </c>
+      <c r="C77">
+        <v>16.51553507186125</v>
+      </c>
+      <c r="D77">
+        <v>47.40803507186125</v>
+      </c>
+      <c r="E77">
+        <v>30.9125</v>
+      </c>
+      <c r="F77">
+        <v>34.4625</v>
+      </c>
+      <c r="G77">
+        <v>3.57</v>
+      </c>
+      <c r="H77">
+        <v>42.4</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>21.8</v>
+      </c>
+      <c r="K77">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L77">
+        <v>21.5</v>
+      </c>
+      <c r="M77">
+        <v>1.57493625</v>
+      </c>
+      <c r="N77">
+        <v>19.92506375</v>
+      </c>
+      <c r="O77">
+        <v>5.778268487500001</v>
+      </c>
+      <c r="P77">
+        <v>14.1467952625</v>
+      </c>
+      <c r="Q77">
+        <v>14.4467952625</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3672358789667393</v>
+      </c>
+      <c r="T77">
+        <v>1.741756336716817</v>
+      </c>
+      <c r="U77">
+        <v>0.0457</v>
+      </c>
+      <c r="V77">
+        <v>0.29</v>
+      </c>
+      <c r="W77">
+        <v>0.032447</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>13.65134620528291</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1157763881285847</v>
+      </c>
+      <c r="C78">
+        <v>16.12397183729691</v>
+      </c>
+      <c r="D78">
+        <v>47.4759718372969</v>
+      </c>
+      <c r="E78">
+        <v>31.372</v>
+      </c>
+      <c r="F78">
+        <v>34.922</v>
+      </c>
+      <c r="G78">
+        <v>3.57</v>
+      </c>
+      <c r="H78">
+        <v>42.4</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>21.8</v>
+      </c>
+      <c r="K78">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L78">
+        <v>21.5</v>
+      </c>
+      <c r="M78">
+        <v>1.5959354</v>
+      </c>
+      <c r="N78">
+        <v>19.9040646</v>
+      </c>
+      <c r="O78">
+        <v>5.772178734000001</v>
+      </c>
+      <c r="P78">
+        <v>14.131885866</v>
+      </c>
+      <c r="Q78">
+        <v>14.431885866</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3796527838691027</v>
+      </c>
+      <c r="T78">
+        <v>1.807605484697059</v>
+      </c>
+      <c r="U78">
+        <v>0.0457</v>
+      </c>
+      <c r="V78">
+        <v>0.29</v>
+      </c>
+      <c r="W78">
+        <v>0.032447</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>13.47172322889761</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1154085565154845</v>
+      </c>
+      <c r="C79">
+        <v>15.73260359193887</v>
+      </c>
+      <c r="D79">
+        <v>47.54410359193886</v>
+      </c>
+      <c r="E79">
+        <v>31.83149999999999</v>
+      </c>
+      <c r="F79">
+        <v>35.3815</v>
+      </c>
+      <c r="G79">
+        <v>3.57</v>
+      </c>
+      <c r="H79">
+        <v>42.4</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>21.8</v>
+      </c>
+      <c r="K79">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L79">
+        <v>21.5</v>
+      </c>
+      <c r="M79">
+        <v>1.61693455</v>
+      </c>
+      <c r="N79">
+        <v>19.88306545</v>
+      </c>
+      <c r="O79">
+        <v>5.766088980500001</v>
+      </c>
+      <c r="P79">
+        <v>14.1169764695</v>
+      </c>
+      <c r="Q79">
+        <v>14.4169764695</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3931494196325412</v>
+      </c>
+      <c r="T79">
+        <v>1.879180645545148</v>
+      </c>
+      <c r="U79">
+        <v>0.0457</v>
+      </c>
+      <c r="V79">
+        <v>0.29</v>
+      </c>
+      <c r="W79">
+        <v>0.032447</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>13.29676578436647</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1150407249023843</v>
+      </c>
+      <c r="C80">
+        <v>15.34143117646813</v>
+      </c>
+      <c r="D80">
+        <v>47.61243117646814</v>
+      </c>
+      <c r="E80">
+        <v>32.291</v>
+      </c>
+      <c r="F80">
+        <v>35.841</v>
+      </c>
+      <c r="G80">
+        <v>3.57</v>
+      </c>
+      <c r="H80">
+        <v>42.4</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>21.8</v>
+      </c>
+      <c r="K80">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L80">
+        <v>21.5</v>
+      </c>
+      <c r="M80">
+        <v>1.6379337</v>
+      </c>
+      <c r="N80">
+        <v>19.8620663</v>
+      </c>
+      <c r="O80">
+        <v>5.759999227000001</v>
+      </c>
+      <c r="P80">
+        <v>14.102067073</v>
+      </c>
+      <c r="Q80">
+        <v>14.402067073</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.407873022283565</v>
+      </c>
+      <c r="T80">
+        <v>1.957262639197609</v>
+      </c>
+      <c r="U80">
+        <v>0.0457</v>
+      </c>
+      <c r="V80">
+        <v>0.29</v>
+      </c>
+      <c r="W80">
+        <v>0.032447</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>13.12629442815664</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1146728932892841</v>
+      </c>
+      <c r="C81">
+        <v>14.95045543640539</v>
+      </c>
+      <c r="D81">
+        <v>47.68095543640539</v>
+      </c>
+      <c r="E81">
+        <v>32.7505</v>
+      </c>
+      <c r="F81">
+        <v>36.3005</v>
+      </c>
+      <c r="G81">
+        <v>3.57</v>
+      </c>
+      <c r="H81">
+        <v>42.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>21.8</v>
+      </c>
+      <c r="K81">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L81">
+        <v>21.5</v>
+      </c>
+      <c r="M81">
+        <v>1.65893285</v>
+      </c>
+      <c r="N81">
+        <v>19.84106715</v>
+      </c>
+      <c r="O81">
+        <v>5.753909473500001</v>
+      </c>
+      <c r="P81">
+        <v>14.0871576765</v>
+      </c>
+      <c r="Q81">
+        <v>14.3871576765</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.423998872806115</v>
+      </c>
+      <c r="T81">
+        <v>2.042781013197923</v>
+      </c>
+      <c r="U81">
+        <v>0.0457</v>
+      </c>
+      <c r="V81">
+        <v>0.29</v>
+      </c>
+      <c r="W81">
+        <v>0.032447</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>12.96013880248378</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1152138616761839</v>
+      </c>
+      <c r="C82">
+        <v>14.39024522518585</v>
+      </c>
+      <c r="D82">
+        <v>47.58024522518585</v>
+      </c>
+      <c r="E82">
+        <v>33.21</v>
+      </c>
+      <c r="F82">
+        <v>36.76</v>
+      </c>
+      <c r="G82">
+        <v>3.57</v>
+      </c>
+      <c r="H82">
+        <v>42.4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>21.8</v>
+      </c>
+      <c r="K82">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L82">
+        <v>21.5</v>
+      </c>
+      <c r="M82">
+        <v>1.738748</v>
+      </c>
+      <c r="N82">
+        <v>19.761252</v>
+      </c>
+      <c r="O82">
+        <v>5.73076308</v>
+      </c>
+      <c r="P82">
+        <v>14.03048892</v>
+      </c>
+      <c r="Q82">
+        <v>14.33048892</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4417373083809198</v>
+      </c>
+      <c r="T82">
+        <v>2.136851224598268</v>
+      </c>
+      <c r="U82">
+        <v>0.0473</v>
+      </c>
+      <c r="V82">
+        <v>0.29</v>
+      </c>
+      <c r="W82">
+        <v>0.033583</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>12.36521911168266</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1148573900630838</v>
+      </c>
+      <c r="C83">
+        <v>13.99706043945333</v>
+      </c>
+      <c r="D83">
+        <v>47.64656043945332</v>
+      </c>
+      <c r="E83">
+        <v>33.6695</v>
+      </c>
+      <c r="F83">
+        <v>37.2195</v>
+      </c>
+      <c r="G83">
+        <v>3.57</v>
+      </c>
+      <c r="H83">
+        <v>42.4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>21.8</v>
+      </c>
+      <c r="K83">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L83">
+        <v>21.5</v>
+      </c>
+      <c r="M83">
+        <v>1.76048235</v>
+      </c>
+      <c r="N83">
+        <v>19.73951765</v>
+      </c>
+      <c r="O83">
+        <v>5.724460118500001</v>
+      </c>
+      <c r="P83">
+        <v>14.0150575315</v>
+      </c>
+      <c r="Q83">
+        <v>14.3150575315</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.461342947700441</v>
+      </c>
+      <c r="T83">
+        <v>2.240823563514439</v>
+      </c>
+      <c r="U83">
+        <v>0.0473</v>
+      </c>
+      <c r="V83">
+        <v>0.29</v>
+      </c>
+      <c r="W83">
+        <v>0.033583</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>12.2125620856125</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1145009184499836</v>
+      </c>
+      <c r="C84">
+        <v>13.60406076607174</v>
+      </c>
+      <c r="D84">
+        <v>47.71306076607174</v>
+      </c>
+      <c r="E84">
+        <v>34.129</v>
+      </c>
+      <c r="F84">
+        <v>37.679</v>
+      </c>
+      <c r="G84">
+        <v>3.57</v>
+      </c>
+      <c r="H84">
+        <v>42.4</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>21.8</v>
+      </c>
+      <c r="K84">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L84">
+        <v>21.5</v>
+      </c>
+      <c r="M84">
+        <v>1.7822167</v>
+      </c>
+      <c r="N84">
+        <v>19.7177833</v>
+      </c>
+      <c r="O84">
+        <v>5.718157157000001</v>
+      </c>
+      <c r="P84">
+        <v>13.999626143</v>
+      </c>
+      <c r="Q84">
+        <v>14.299626143</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4831269913887979</v>
+      </c>
+      <c r="T84">
+        <v>2.356348384532408</v>
+      </c>
+      <c r="U84">
+        <v>0.0473</v>
+      </c>
+      <c r="V84">
+        <v>0.29</v>
+      </c>
+      <c r="W84">
+        <v>0.033583</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>12.06362840164162</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1141444468368834</v>
+      </c>
+      <c r="C85">
+        <v>13.21124698120857</v>
+      </c>
+      <c r="D85">
+        <v>47.77974698120857</v>
+      </c>
+      <c r="E85">
+        <v>34.5885</v>
+      </c>
+      <c r="F85">
+        <v>38.1385</v>
+      </c>
+      <c r="G85">
+        <v>3.57</v>
+      </c>
+      <c r="H85">
+        <v>42.4</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>21.8</v>
+      </c>
+      <c r="K85">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L85">
+        <v>21.5</v>
+      </c>
+      <c r="M85">
+        <v>1.80395105</v>
+      </c>
+      <c r="N85">
+        <v>19.69604895</v>
+      </c>
+      <c r="O85">
+        <v>5.711854195500001</v>
+      </c>
+      <c r="P85">
+        <v>13.9841947545</v>
+      </c>
+      <c r="Q85">
+        <v>14.2841947545</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5074738637463733</v>
+      </c>
+      <c r="T85">
+        <v>2.485464360964254</v>
+      </c>
+      <c r="U85">
+        <v>0.0473</v>
+      </c>
+      <c r="V85">
+        <v>0.29</v>
+      </c>
+      <c r="W85">
+        <v>0.033583</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>11.91828348113991</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1137879752237833</v>
+      </c>
+      <c r="C86">
+        <v>12.81861986537663</v>
+      </c>
+      <c r="D86">
+        <v>47.84661986537662</v>
+      </c>
+      <c r="E86">
+        <v>35.04799999999999</v>
+      </c>
+      <c r="F86">
+        <v>38.59799999999999</v>
+      </c>
+      <c r="G86">
+        <v>3.57</v>
+      </c>
+      <c r="H86">
+        <v>42.4</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>21.8</v>
+      </c>
+      <c r="K86">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L86">
+        <v>21.5</v>
+      </c>
+      <c r="M86">
+        <v>1.8256854</v>
+      </c>
+      <c r="N86">
+        <v>19.6743146</v>
+      </c>
+      <c r="O86">
+        <v>5.705551234000001</v>
+      </c>
+      <c r="P86">
+        <v>13.968763366</v>
+      </c>
+      <c r="Q86">
+        <v>14.268763366</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5348640951486452</v>
+      </c>
+      <c r="T86">
+        <v>2.630719834450081</v>
+      </c>
+      <c r="U86">
+        <v>0.0473</v>
+      </c>
+      <c r="V86">
+        <v>0.29</v>
+      </c>
+      <c r="W86">
+        <v>0.033583</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>11.77639915398349</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1134315036106831</v>
+      </c>
+      <c r="C87">
+        <v>12.42618020346447</v>
+      </c>
+      <c r="D87">
+        <v>47.91368020346447</v>
+      </c>
+      <c r="E87">
+        <v>35.5075</v>
+      </c>
+      <c r="F87">
+        <v>39.0575</v>
+      </c>
+      <c r="G87">
+        <v>3.57</v>
+      </c>
+      <c r="H87">
+        <v>42.4</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>21.8</v>
+      </c>
+      <c r="K87">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L87">
+        <v>21.5</v>
+      </c>
+      <c r="M87">
+        <v>1.84741975</v>
+      </c>
+      <c r="N87">
+        <v>19.65258025</v>
+      </c>
+      <c r="O87">
+        <v>5.6992482725</v>
+      </c>
+      <c r="P87">
+        <v>13.9533319775</v>
+      </c>
+      <c r="Q87">
+        <v>14.2533319775</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5659063574045538</v>
+      </c>
+      <c r="T87">
+        <v>2.795342704400685</v>
+      </c>
+      <c r="U87">
+        <v>0.0473</v>
+      </c>
+      <c r="V87">
+        <v>0.29</v>
+      </c>
+      <c r="W87">
+        <v>0.033583</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>11.63785328158368</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1130750319975829</v>
+      </c>
+      <c r="C88">
+        <v>12.03392878476715</v>
+      </c>
+      <c r="D88">
+        <v>47.98092878476714</v>
+      </c>
+      <c r="E88">
+        <v>35.967</v>
+      </c>
+      <c r="F88">
+        <v>39.517</v>
+      </c>
+      <c r="G88">
+        <v>3.57</v>
+      </c>
+      <c r="H88">
+        <v>42.4</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>21.8</v>
+      </c>
+      <c r="K88">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L88">
+        <v>21.5</v>
+      </c>
+      <c r="M88">
+        <v>1.8691541</v>
+      </c>
+      <c r="N88">
+        <v>19.6308459</v>
+      </c>
+      <c r="O88">
+        <v>5.692945311000001</v>
+      </c>
+      <c r="P88">
+        <v>13.937900589</v>
+      </c>
+      <c r="Q88">
+        <v>14.237900589</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6013832285541636</v>
+      </c>
+      <c r="T88">
+        <v>2.983483127201376</v>
+      </c>
+      <c r="U88">
+        <v>0.0473</v>
+      </c>
+      <c r="V88">
+        <v>0.29</v>
+      </c>
+      <c r="W88">
+        <v>0.033583</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>11.50252940621643</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1127185603844827</v>
+      </c>
+      <c r="C89">
+        <v>11.64186640301716</v>
+      </c>
+      <c r="D89">
+        <v>48.04836640301716</v>
+      </c>
+      <c r="E89">
+        <v>36.4265</v>
+      </c>
+      <c r="F89">
+        <v>39.97649999999999</v>
+      </c>
+      <c r="G89">
+        <v>3.57</v>
+      </c>
+      <c r="H89">
+        <v>42.4</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>21.8</v>
+      </c>
+      <c r="K89">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L89">
+        <v>21.5</v>
+      </c>
+      <c r="M89">
+        <v>1.89088845</v>
+      </c>
+      <c r="N89">
+        <v>19.60911155</v>
+      </c>
+      <c r="O89">
+        <v>5.686642349500001</v>
+      </c>
+      <c r="P89">
+        <v>13.9224692005</v>
+      </c>
+      <c r="Q89">
+        <v>14.2224692005</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.6423180798806363</v>
+      </c>
+      <c r="T89">
+        <v>3.200568230432942</v>
+      </c>
+      <c r="U89">
+        <v>0.0473</v>
+      </c>
+      <c r="V89">
+        <v>0.29</v>
+      </c>
+      <c r="W89">
+        <v>0.033583</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>11.37031642453578</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1123620887713826</v>
+      </c>
+      <c r="C90">
+        <v>11.24999385641566</v>
+      </c>
+      <c r="D90">
+        <v>48.11599385641566</v>
+      </c>
+      <c r="E90">
+        <v>36.886</v>
+      </c>
+      <c r="F90">
+        <v>40.436</v>
+      </c>
+      <c r="G90">
+        <v>3.57</v>
+      </c>
+      <c r="H90">
+        <v>42.4</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>21.8</v>
+      </c>
+      <c r="K90">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L90">
+        <v>21.5</v>
+      </c>
+      <c r="M90">
+        <v>1.9126228</v>
+      </c>
+      <c r="N90">
+        <v>19.5873772</v>
+      </c>
+      <c r="O90">
+        <v>5.680339388</v>
+      </c>
+      <c r="P90">
+        <v>13.907037812</v>
+      </c>
+      <c r="Q90">
+        <v>14.207037812</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.690075406428188</v>
+      </c>
+      <c r="T90">
+        <v>3.453834184203103</v>
+      </c>
+      <c r="U90">
+        <v>0.0473</v>
+      </c>
+      <c r="V90">
+        <v>0.29</v>
+      </c>
+      <c r="W90">
+        <v>0.033583</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>11.24110828334787</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1120056171582824</v>
+      </c>
+      <c r="C91">
+        <v>10.85831194766399</v>
+      </c>
+      <c r="D91">
+        <v>48.18381194766399</v>
+      </c>
+      <c r="E91">
+        <v>37.3455</v>
+      </c>
+      <c r="F91">
+        <v>40.8955</v>
+      </c>
+      <c r="G91">
+        <v>3.57</v>
+      </c>
+      <c r="H91">
+        <v>42.4</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>21.8</v>
+      </c>
+      <c r="K91">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L91">
+        <v>21.5</v>
+      </c>
+      <c r="M91">
+        <v>1.93435715</v>
+      </c>
+      <c r="N91">
+        <v>19.56564285</v>
+      </c>
+      <c r="O91">
+        <v>5.674036426500001</v>
+      </c>
+      <c r="P91">
+        <v>13.8916064235</v>
+      </c>
+      <c r="Q91">
+        <v>14.1916064235</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7465158832571126</v>
+      </c>
+      <c r="T91">
+        <v>3.753148493204202</v>
+      </c>
+      <c r="U91">
+        <v>0.0473</v>
+      </c>
+      <c r="V91">
+        <v>0.29</v>
+      </c>
+      <c r="W91">
+        <v>0.033583</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>11.11480369589452</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1116491455451822</v>
+      </c>
+      <c r="C92">
+        <v>10.46682148399539</v>
+      </c>
+      <c r="D92">
+        <v>48.25182148399539</v>
+      </c>
+      <c r="E92">
+        <v>37.805</v>
+      </c>
+      <c r="F92">
+        <v>41.355</v>
+      </c>
+      <c r="G92">
+        <v>3.57</v>
+      </c>
+      <c r="H92">
+        <v>42.4</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>21.8</v>
+      </c>
+      <c r="K92">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L92">
+        <v>21.5</v>
+      </c>
+      <c r="M92">
+        <v>1.9560915</v>
+      </c>
+      <c r="N92">
+        <v>19.5439085</v>
+      </c>
+      <c r="O92">
+        <v>5.667733465000001</v>
+      </c>
+      <c r="P92">
+        <v>13.876175035</v>
+      </c>
+      <c r="Q92">
+        <v>14.176175035</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8142444554518222</v>
+      </c>
+      <c r="T92">
+        <v>4.112325664005521</v>
+      </c>
+      <c r="U92">
+        <v>0.0473</v>
+      </c>
+      <c r="V92">
+        <v>0.29</v>
+      </c>
+      <c r="W92">
+        <v>0.033583</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>10.99130587705125</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.111292673932082</v>
+      </c>
+      <c r="C93">
+        <v>10.07552327720708</v>
+      </c>
+      <c r="D93">
+        <v>48.32002327720708</v>
+      </c>
+      <c r="E93">
+        <v>38.2645</v>
+      </c>
+      <c r="F93">
+        <v>41.8145</v>
+      </c>
+      <c r="G93">
+        <v>3.57</v>
+      </c>
+      <c r="H93">
+        <v>42.4</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>21.8</v>
+      </c>
+      <c r="K93">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L93">
+        <v>21.5</v>
+      </c>
+      <c r="M93">
+        <v>1.97782585</v>
+      </c>
+      <c r="N93">
+        <v>19.52217415</v>
+      </c>
+      <c r="O93">
+        <v>5.661430503500001</v>
+      </c>
+      <c r="P93">
+        <v>13.8607436465</v>
+      </c>
+      <c r="Q93">
+        <v>14.1607436465</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8970238214675785</v>
+      </c>
+      <c r="T93">
+        <v>4.551319983873801</v>
+      </c>
+      <c r="U93">
+        <v>0.0473</v>
+      </c>
+      <c r="V93">
+        <v>0.29</v>
+      </c>
+      <c r="W93">
+        <v>0.033583</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>10.87052229598476</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1109362023189819</v>
+      </c>
+      <c r="C94">
+        <v>9.684418143692511</v>
+      </c>
+      <c r="D94">
+        <v>48.38841814369251</v>
+      </c>
+      <c r="E94">
+        <v>38.724</v>
+      </c>
+      <c r="F94">
+        <v>42.274</v>
+      </c>
+      <c r="G94">
+        <v>3.57</v>
+      </c>
+      <c r="H94">
+        <v>42.4</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>21.8</v>
+      </c>
+      <c r="K94">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L94">
+        <v>21.5</v>
+      </c>
+      <c r="M94">
+        <v>1.9995602</v>
+      </c>
+      <c r="N94">
+        <v>19.5004398</v>
+      </c>
+      <c r="O94">
+        <v>5.655127542000001</v>
+      </c>
+      <c r="P94">
+        <v>13.845312258</v>
+      </c>
+      <c r="Q94">
+        <v>14.145312258</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.000498028987274</v>
+      </c>
+      <c r="T94">
+        <v>5.10006288370915</v>
+      </c>
+      <c r="U94">
+        <v>0.0473</v>
+      </c>
+      <c r="V94">
+        <v>0.29</v>
+      </c>
+      <c r="W94">
+        <v>0.033583</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>10.75236444494144</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1105797307058817</v>
+      </c>
+      <c r="C95">
+        <v>9.293506904473986</v>
+      </c>
+      <c r="D95">
+        <v>48.45700690447399</v>
+      </c>
+      <c r="E95">
+        <v>39.1835</v>
+      </c>
+      <c r="F95">
+        <v>42.7335</v>
+      </c>
+      <c r="G95">
+        <v>3.57</v>
+      </c>
+      <c r="H95">
+        <v>42.4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>21.8</v>
+      </c>
+      <c r="K95">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L95">
+        <v>21.5</v>
+      </c>
+      <c r="M95">
+        <v>2.02129455</v>
+      </c>
+      <c r="N95">
+        <v>19.47870545</v>
+      </c>
+      <c r="O95">
+        <v>5.6488245805</v>
+      </c>
+      <c r="P95">
+        <v>13.8298808695</v>
+      </c>
+      <c r="Q95">
+        <v>14.1298808695</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.13353629579831</v>
+      </c>
+      <c r="T95">
+        <v>5.805589469211741</v>
+      </c>
+      <c r="U95">
+        <v>0.0473</v>
+      </c>
+      <c r="V95">
+        <v>0.29</v>
+      </c>
+      <c r="W95">
+        <v>0.033583</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>10.63674762295283</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1102232590927815</v>
+      </c>
+      <c r="C96">
+        <v>8.902790385235463</v>
+      </c>
+      <c r="D96">
+        <v>48.52579038523546</v>
+      </c>
+      <c r="E96">
+        <v>39.643</v>
+      </c>
+      <c r="F96">
+        <v>43.193</v>
+      </c>
+      <c r="G96">
+        <v>3.57</v>
+      </c>
+      <c r="H96">
+        <v>42.4</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>21.8</v>
+      </c>
+      <c r="K96">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L96">
+        <v>21.5</v>
+      </c>
+      <c r="M96">
+        <v>2.0430289</v>
+      </c>
+      <c r="N96">
+        <v>19.4569711</v>
+      </c>
+      <c r="O96">
+        <v>5.642521619000001</v>
+      </c>
+      <c r="P96">
+        <v>13.814449481</v>
+      </c>
+      <c r="Q96">
+        <v>14.114449481</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.31092065154636</v>
+      </c>
+      <c r="T96">
+        <v>6.746291583215197</v>
+      </c>
+      <c r="U96">
+        <v>0.0473</v>
+      </c>
+      <c r="V96">
+        <v>0.29</v>
+      </c>
+      <c r="W96">
+        <v>0.033583</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>10.52359073334694</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1098667874796813</v>
+      </c>
+      <c r="C97">
+        <v>8.512269416355707</v>
+      </c>
+      <c r="D97">
+        <v>48.5947694163557</v>
+      </c>
+      <c r="E97">
+        <v>40.1025</v>
+      </c>
+      <c r="F97">
+        <v>43.6525</v>
+      </c>
+      <c r="G97">
+        <v>3.57</v>
+      </c>
+      <c r="H97">
+        <v>42.4</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>21.8</v>
+      </c>
+      <c r="K97">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L97">
+        <v>21.5</v>
+      </c>
+      <c r="M97">
+        <v>2.06476325</v>
+      </c>
+      <c r="N97">
+        <v>19.43523675</v>
+      </c>
+      <c r="O97">
+        <v>5.636218657500002</v>
+      </c>
+      <c r="P97">
+        <v>13.7990180925</v>
+      </c>
+      <c r="Q97">
+        <v>14.0990180925</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.559258749593629</v>
+      </c>
+      <c r="T97">
+        <v>8.063274542820038</v>
+      </c>
+      <c r="U97">
+        <v>0.0473</v>
+      </c>
+      <c r="V97">
+        <v>0.29</v>
+      </c>
+      <c r="W97">
+        <v>0.033583</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>10.41281609404856</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1095103158665812</v>
+      </c>
+      <c r="C98">
+        <v>8.12194483294175</v>
+      </c>
+      <c r="D98">
+        <v>48.66394483294174</v>
+      </c>
+      <c r="E98">
+        <v>40.562</v>
+      </c>
+      <c r="F98">
+        <v>44.11199999999999</v>
+      </c>
+      <c r="G98">
+        <v>3.57</v>
+      </c>
+      <c r="H98">
+        <v>42.4</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>21.8</v>
+      </c>
+      <c r="K98">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L98">
+        <v>21.5</v>
+      </c>
+      <c r="M98">
+        <v>2.0864976</v>
+      </c>
+      <c r="N98">
+        <v>19.4135024</v>
+      </c>
+      <c r="O98">
+        <v>5.629915696</v>
+      </c>
+      <c r="P98">
+        <v>13.783586704</v>
+      </c>
+      <c r="Q98">
+        <v>14.083586704</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.931765896664527</v>
+      </c>
+      <c r="T98">
+        <v>10.03874898222727</v>
+      </c>
+      <c r="U98">
+        <v>0.0473</v>
+      </c>
+      <c r="V98">
+        <v>0.29</v>
+      </c>
+      <c r="W98">
+        <v>0.033583</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>10.30434925973555</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.111770904253481</v>
+      </c>
+      <c r="C99">
+        <v>7.227070136552506</v>
+      </c>
+      <c r="D99">
+        <v>48.2285701365525</v>
+      </c>
+      <c r="E99">
+        <v>41.0215</v>
+      </c>
+      <c r="F99">
+        <v>44.57149999999999</v>
+      </c>
+      <c r="G99">
+        <v>3.57</v>
+      </c>
+      <c r="H99">
+        <v>42.4</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>21.8</v>
+      </c>
+      <c r="K99">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L99">
+        <v>21.5</v>
+      </c>
+      <c r="M99">
+        <v>2.27760365</v>
+      </c>
+      <c r="N99">
+        <v>19.22239635</v>
+      </c>
+      <c r="O99">
+        <v>5.574494941500001</v>
+      </c>
+      <c r="P99">
+        <v>13.6479014085</v>
+      </c>
+      <c r="Q99">
+        <v>13.9479014085</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.552611141782698</v>
+      </c>
+      <c r="T99">
+        <v>13.33120638123936</v>
+      </c>
+      <c r="U99">
+        <v>0.0511</v>
+      </c>
+      <c r="V99">
+        <v>0.29</v>
+      </c>
+      <c r="W99">
+        <v>0.036281</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>9.439746024291805</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1114414126403808</v>
+      </c>
+      <c r="C100">
+        <v>6.830542475325522</v>
+      </c>
+      <c r="D100">
+        <v>48.29154247532551</v>
+      </c>
+      <c r="E100">
+        <v>41.48099999999999</v>
+      </c>
+      <c r="F100">
+        <v>45.03099999999999</v>
+      </c>
+      <c r="G100">
+        <v>3.57</v>
+      </c>
+      <c r="H100">
+        <v>42.4</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>21.8</v>
+      </c>
+      <c r="K100">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L100">
+        <v>21.5</v>
+      </c>
+      <c r="M100">
+        <v>2.3010841</v>
+      </c>
+      <c r="N100">
+        <v>19.1989159</v>
+      </c>
+      <c r="O100">
+        <v>5.567685611000001</v>
+      </c>
+      <c r="P100">
+        <v>13.631230289</v>
+      </c>
+      <c r="Q100">
+        <v>13.931230289</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.794301632019038</v>
+      </c>
+      <c r="T100">
+        <v>19.91612117926353</v>
+      </c>
+      <c r="U100">
+        <v>0.0511</v>
+      </c>
+      <c r="V100">
+        <v>0.29</v>
+      </c>
+      <c r="W100">
+        <v>0.036281</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>9.343422085268418</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1111119210272807</v>
+      </c>
+      <c r="C101">
+        <v>6.434179475833545</v>
+      </c>
+      <c r="D101">
+        <v>48.35467947583354</v>
+      </c>
+      <c r="E101">
+        <v>41.9405</v>
+      </c>
+      <c r="F101">
+        <v>45.4905</v>
+      </c>
+      <c r="G101">
+        <v>3.57</v>
+      </c>
+      <c r="H101">
+        <v>42.4</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>21.8</v>
+      </c>
+      <c r="K101">
+        <v>0.3000000000000007</v>
+      </c>
+      <c r="L101">
+        <v>21.5</v>
+      </c>
+      <c r="M101">
+        <v>2.32456455</v>
+      </c>
+      <c r="N101">
+        <v>19.17543545</v>
+      </c>
+      <c r="O101">
+        <v>5.560876280500001</v>
+      </c>
+      <c r="P101">
+        <v>13.6145591695</v>
+      </c>
+      <c r="Q101">
+        <v>13.9145591695</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.519373102728058</v>
+      </c>
+      <c r="T101">
+        <v>39.67086557333604</v>
+      </c>
+      <c r="U101">
+        <v>0.0511</v>
+      </c>
+      <c r="V101">
+        <v>0.29</v>
+      </c>
+      <c r="W101">
+        <v>0.036281</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>9.249044084407123</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
